--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -2,26 +2,24 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet name="branch_exceptions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Carlito"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Carlito"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
     </font>
     <font>
@@ -30,54 +28,39 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -337,6 +320,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -346,12 +331,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:J47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="12" customWidth="1" style="9" min="1" max="1"/>
-    <col width="65" customWidth="1" style="9" min="2" max="2"/>
-    <col width="110" customWidth="1" style="9" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="65" customWidth="1" min="2" max="2"/>
+    <col width="32.83203125" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -400,6 +385,11 @@
           <t>ninth_reference_average_pj_per_year_all_economies</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>relevance_audit</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="b">
@@ -412,7 +402,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>The sector-split aggregated-demand workflow can produce a small Other sector amount for this fuel, but the economy templates do not expose that branch; the values are immaterial and are intentionally left out. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Other sector\Other recovered gases (sector='Other sector'; 9th sector='Other sector')</t>
+          <t>The sector-split aggregated-demand workflow can produce a small Other sector amount for this fuel, but the economy templates do not expose that branch; the values are immaterial and are intentionally left out. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Other sector\Other recovered gases (sector='Other sector'; 9th sector='Other sector') Relevance audit: 2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -425,14 +415,27 @@
           <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -441,23 +444,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A small stock-change value can be present in the source data, but the current economy templates do not expose this branch; it is intentionally left out as immaterial. Materiality mapping needs review: Cannot derive source mapping for registry path: Stock Changes\Secondary\Bio jet kerosene</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
-        </is>
-      </c>
+          <t>A small stock-change value can be present in the source data, but the current economy templates do not expose this branch; it is intentionally left out as immaterial. Materiality mapping needs review: Cannot derive source mapping for registry path: Stock Changes\Secondary\Bio jet kerosene Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-    </row>
-    <row r="4" ht="32" customHeight="1" s="9">
+      <c r="F3" t="n">
+        <v>-0.042852</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.042873</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -466,23 +478,32 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Additives and oxygenates (sector='CHP interim'; 9th sector='CHP interim')</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
-        </is>
-      </c>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Additives and oxygenates (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-    </row>
-    <row r="5" ht="32" customHeight="1" s="9">
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -491,23 +512,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim')</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
-        </is>
-      </c>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1" s="9">
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-4.809293</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.311189828000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
       <c r="A6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -516,23 +546,32 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat (sector='Electricity interim'; fuel='Heat'; 9th sector='Electricity interim')</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
-        </is>
-      </c>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat (sector='Electricity interim'; fuel='Heat'; 9th sector='Electricity interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1" s="9">
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1704.741122</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1">
       <c r="A7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -541,31 +580,32 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
-        </is>
-      </c>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-3.060635</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-2.743651908</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" ht="32" customHeight="1" s="9">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1">
       <c r="A8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -574,19 +614,1478 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products')</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
-        </is>
-      </c>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.1022</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.102199788</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Non Energy Use\Blast furnace gas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Blast furnace gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Non Energy Use\Gas works gas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Gas works gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Non Energy Use\Hydrogen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Hydrogen (sector='Non Energy Use'; fuel='Hydrogen'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>01_AUS|05_PRC|10_MAS|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Non Energy Use\Other recovered gases</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Other recovered gases (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Anthracite</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>05_PRC|20_USA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>01_AUS|05_PRC|16_RUS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.080882</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.051718465952</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4.153502928239663</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Blast furnace gas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>-0.550146</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-4.153502928239663</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Lignite</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>05_PRC|12_NZ|16_RUS|20_USA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.096146</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.124281404</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Lubricants</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Other recovered gases</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-4.153502928239663</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Patent fuel</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16_RUS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-4.153502928239663</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Petroleum coke</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>-0.101551</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.086408044</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Refinery gas not liquefied</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.499257</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.48048051744</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coal tar</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>-0.06029</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>01_AUS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="b">
+        <v>1</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lignite</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>05_PRC|16_RUS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Non specified own uses\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>01_AUS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="b">
+        <v>1</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Non specified own uses\Crude oil</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>01_AUS|16_RUS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Anthracite</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="b">
+        <v>1</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="b">
+        <v>1</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Coke oven coke</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="b">
+        <v>1</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Gas works gas</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="b">
+        <v>1</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Lignite</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="b">
+        <v>1</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Lubricants</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="b">
+        <v>1</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>01_AUS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="b">
+        <v>1</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-37.58266388971636</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="b">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Lignite</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>16_RUS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="b">
+        <v>1</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>19_THA</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="b">
+        <v>1</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Other bituminous coal</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>05_PRC|16_RUS</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>-0.133298</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="b">
+        <v>1</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Peat</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>16_RUS</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="b">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>16_RUS</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -600,67 +2099,67 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="22" customWidth="1" style="9" min="1" max="1"/>
-    <col width="110" customWidth="1" style="9" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="8" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Reviewed baseline-seed validation exceptions.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Source of truth</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>The enabled rows in branch_exceptions.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Exceptions match by branch path and apply across economies.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Use</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>Only add a row when the branch is intentionally absent from the template and the values are immaterial or outside the current modelled scope.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Review</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Keep the reason in notes so the exception remains auditable.</t>
         </is>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -3,14 +3,17 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="branch_exceptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="README" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'branch_exceptions'!$A$1:$J$47</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -331,7 +334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -390,6 +393,11 @@
           <t>relevance_audit</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>zero filter</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="b">
@@ -415,21 +423,18 @@
           <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -466,6 +471,11 @@
           <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>DISABLED — no trigger across audited vintages</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" t="b">
@@ -500,6 +510,11 @@
           <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>DISABLED — no trigger across audited vintages</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="32" customHeight="1">
       <c r="A5" t="b">
@@ -534,6 +549,11 @@
           <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>DISABLED — no trigger across audited vintages</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="32" customHeight="1">
       <c r="A6" t="b">
@@ -568,6 +588,11 @@
           <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>DISABLED — no trigger across audited vintages</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="32" customHeight="1">
       <c r="A7" t="b">
@@ -602,6 +627,11 @@
           <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>DISABLED — no trigger across audited vintages</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="32" customHeight="1">
       <c r="A8" t="b">
@@ -634,6 +664,11 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>DISABLED — no trigger across audited vintages</t>
         </is>
       </c>
     </row>
@@ -666,6 +701,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="b">
@@ -696,6 +736,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="b">
@@ -726,6 +771,11 @@
           <t>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="b">
@@ -756,6 +806,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="b">
@@ -777,21 +832,18 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -830,6 +882,11 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -870,6 +927,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="b">
@@ -908,6 +970,11 @@
           <t>2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="b">
@@ -929,21 +996,18 @@
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -984,6 +1048,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="b">
@@ -1020,6 +1089,11 @@
       <c r="J19" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -1060,6 +1134,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="b">
@@ -1081,21 +1160,18 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1119,21 +1195,18 @@
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1174,6 +1247,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="b">
@@ -1195,21 +1273,18 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1233,21 +1308,18 @@
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1288,6 +1360,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="b">
@@ -1309,21 +1386,18 @@
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1347,21 +1421,18 @@
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1385,21 +1456,18 @@
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1423,21 +1491,18 @@
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1461,21 +1526,18 @@
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1499,21 +1561,18 @@
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1537,21 +1596,18 @@
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1575,21 +1631,18 @@
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1613,21 +1666,18 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1651,21 +1701,18 @@
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1689,21 +1736,18 @@
         </is>
       </c>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1727,21 +1771,18 @@
         </is>
       </c>
       <c r="E38" t="inlineStr"/>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1765,21 +1806,18 @@
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1803,21 +1841,18 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1841,21 +1876,18 @@
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1896,6 +1928,11 @@
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="b">
@@ -1917,21 +1954,18 @@
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1955,21 +1989,18 @@
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -2010,6 +2041,11 @@
           <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="b">
@@ -2031,21 +2067,18 @@
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -2069,6 +2102,1884 @@
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J47"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>enabled</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>branch_path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>economies_that_need_it</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>economies_resolved_in_templates</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>esto_2024_last_year_signed_pj_all_economies</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>esto_2025_last_year_signed_pj_all_economies</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>esto_2026_last_year_signed_pj_all_economies</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ninth_reference_average_pj_per_year_all_economies</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>relevance_audit</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>zero filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="b">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Other sector\Other recovered gases</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>The sector-split aggregated-demand workflow can produce a small Other sector amount for this fuel, but the economy templates do not expose that branch; the values are immaterial and are intentionally left out. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Other sector\Other recovered gases (sector='Other sector'; 9th sector='Other sector') Relevance audit: 2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12_NZ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</t>
+        </is>
+      </c>
+      <c r="K2">
+        <f>AND(F2=0,G2=0,H2=0,I2=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Stock Changes\Secondary\Bio jet kerosene</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A small stock-change value can be present in the source data, but the current economy templates do not expose this branch; it is intentionally left out as immaterial. Materiality mapping needs review: Cannot derive source mapping for registry path: Stock Changes\Secondary\Bio jet kerosene Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>-0.042852</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.042873</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K3">
+        <f>AND(F3=0,G3=0,H3=0,I3=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="b">
+        <v>0</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Additives and oxygenates</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Additives and oxygenates (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K4">
+        <f>AND(F4=0,G4=0,H4=0,I4=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="b">
+        <v>0</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-4.809293</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-4.311189828000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K5">
+        <f>AND(F5=0,G5=0,H5=0,I5=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="b">
+        <v>0</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat (sector='Electricity interim'; fuel='Heat'; 9th sector='Electricity interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-1704.741122</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K6">
+        <f>AND(F6=0,G6=0,H6=0,I6=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="b">
+        <v>0</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-3.060635</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-2.743651908</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K7">
+        <f>AND(F7=0,G7=0,H7=0,I7=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="b">
+        <v>0</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.1022</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.102199788</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K8">
+        <f>AND(F8=0,G8=0,H8=0,I8=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="b">
+        <v>1</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Non Energy Use\Blast furnace gas</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Blast furnace gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K9">
+        <f>AND(F9=0,G9=0,H9=0,I9=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="b">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Non Energy Use\Gas works gas</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Gas works gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K10">
+        <f>AND(F10=0,G10=0,H10=0,I10=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="b">
+        <v>1</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Non Energy Use\Hydrogen</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Hydrogen (sector='Non Energy Use'; fuel='Hydrogen'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>01_AUS|05_PRC|10_MAS|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K11">
+        <f>AND(F11=0,G11=0,H11=0,I11=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="b">
+        <v>1</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Non Energy Use\Other recovered gases</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Other recovered gases (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K12">
+        <f>AND(F12=0,G12=0,H12=0,I12=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="b">
+        <v>1</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Anthracite</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>05_PRC|20_USA</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
+        </is>
+      </c>
+      <c r="K13">
+        <f>AND(F13=0,G13=0,H13=0,I13=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="b">
+        <v>1</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>01_AUS|05_PRC|16_RUS</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-1.080882</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-1.051718465952</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-4.153502928239663</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K14">
+        <f>AND(F14=0,G14=0,H14=0,I14=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="b">
+        <v>1</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Blast furnace gas</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.550146</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-4.153502928239663</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K15">
+        <f>AND(F15=0,G15=0,H15=0,I15=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Lignite</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>05_PRC|12_NZ|16_RUS|20_USA</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-1.096146</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-1.124281404</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K16">
+        <f>AND(F16=0,G16=0,H16=0,I16=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Lubricants</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K17">
+        <f>AND(F17=0,G17=0,H17=0,I17=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="b">
+        <v>1</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Other recovered gases</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-4.153502928239663</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K18">
+        <f>AND(F18=0,G18=0,H18=0,I18=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="b">
+        <v>1</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Patent fuel</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16_RUS</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-4.153502928239663</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K19">
+        <f>AND(F19=0,G19=0,H19=0,I19=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="b">
+        <v>1</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Petroleum coke</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>-0.101551</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-2.086408044</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K20">
+        <f>AND(F20=0,G20=0,H20=0,I20=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="b">
+        <v>1</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Coal mines\Refinery gas not liquefied</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K21">
+        <f>AND(F21=0,G21=0,H21=0,I21=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K22">
+        <f>AND(F22=0,G22=0,H22=0,I22=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="b">
+        <v>1</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-0.499257</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.48048051744</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K23">
+        <f>AND(F23=0,G23=0,H23=0,I23=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="b">
+        <v>1</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K24">
+        <f>AND(F24=0,G24=0,H24=0,I24=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="b">
+        <v>1</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K25">
+        <f>AND(F25=0,G25=0,H25=0,I25=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="b">
+        <v>1</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coal tar</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.06029</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K26">
+        <f>AND(F26=0,G26=0,H26=0,I26=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="b">
+        <v>1</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K27">
+        <f>AND(F27=0,G27=0,H27=0,I27=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="b">
+        <v>1</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K28">
+        <f>AND(F28=0,G28=0,H28=0,I28=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="b">
+        <v>1</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>01_AUS</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="K29">
+        <f>AND(F29=0,G29=0,H29=0,I29=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="b">
+        <v>1</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lignite</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>05_PRC|16_RUS</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K30">
+        <f>AND(F30=0,G30=0,H30=0,I30=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="b">
+        <v>1</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K31">
+        <f>AND(F31=0,G31=0,H31=0,I31=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="b">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K32">
+        <f>AND(F32=0,G32=0,H32=0,I32=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="b">
+        <v>1</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Non specified own uses\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>01_AUS</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="K33">
+        <f>AND(F33=0,G33=0,H33=0,I33=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="b">
+        <v>1</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Non specified own uses\Crude oil</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>01_AUS|16_RUS</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K34">
+        <f>AND(F34=0,G34=0,H34=0,I34=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="b">
+        <v>1</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Anthracite</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K35">
+        <f>AND(F35=0,G35=0,H35=0,I35=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="b">
+        <v>1</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K36">
+        <f>AND(F36=0,G36=0,H36=0,I36=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="b">
+        <v>1</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Coke oven coke</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K37">
+        <f>AND(F37=0,G37=0,H37=0,I37=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="b">
+        <v>1</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Gas works gas</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K38">
+        <f>AND(F38=0,G38=0,H38=0,I38=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="b">
+        <v>1</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Lignite</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K39">
+        <f>AND(F39=0,G39=0,H39=0,I39=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="b">
+        <v>1</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Lubricants</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K40">
+        <f>AND(F40=0,G40=0,H40=0,I40=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="b">
+        <v>1</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>01_AUS</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+        </is>
+      </c>
+      <c r="K41">
+        <f>AND(F41=0,G41=0,H41=0,I41=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="b">
+        <v>1</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\BKB and PB</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-37.58266388971636</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+        </is>
+      </c>
+      <c r="K42">
+        <f>AND(F42=0,G42=0,H42=0,I42=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="b">
+        <v>1</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Lignite</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>16_RUS</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K43">
+        <f>AND(F43=0,G43=0,H43=0,I43=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="b">
+        <v>1</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>19_THA</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
+        </is>
+      </c>
+      <c r="K44">
+        <f>AND(F44=0,G44=0,H44=0,I44=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="b">
+        <v>1</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Other bituminous coal</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>05_PRC|16_RUS</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>-0.133298</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K45">
+        <f>AND(F45=0,G45=0,H45=0,I45=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="b">
+        <v>1</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Peat</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>16_RUS</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="K46">
+        <f>AND(F46=0,G46=0,H46=0,I46=0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="b">
+        <v>1</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>16_RUS</t>
+        </is>
+      </c>
       <c r="F47" t="n">
         <v>0</v>
       </c>
@@ -2085,6 +3996,10 @@
         <is>
           <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
+      </c>
+      <c r="K47">
+        <f>AND(F47=0,G47=0,H47=0,I47=0)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -2092,7 +4007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -7,8 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="branch_exceptions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="README" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'branch_exceptions'!$A$1:$J$47</definedName>
@@ -692,10 +691,18 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1829.600277551402</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -703,7 +710,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -762,10 +769,18 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>587.5590317558863</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
@@ -773,7 +788,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -797,10 +812,18 @@
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1829.600277551402</v>
+      </c>
       <c r="J12" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -808,7 +831,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -832,10 +855,18 @@
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-238.4785316762984</v>
+      </c>
       <c r="J13" t="inlineStr">
         <is>
           <t>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
@@ -843,7 +874,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -987,7 +1018,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Lubricants')</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1151,7 +1182,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Refinery gas not liquefied (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Refinery gas not liquefied')</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1186,7 +1217,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Anthracite')</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1264,7 +1295,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Bitumen')</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1299,7 +1330,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Blast furnace gas')</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1377,7 +1408,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Coking coal')</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1412,7 +1443,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Gas works gas')</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1447,7 +1478,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Kerosene type jet fuel')</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1482,7 +1513,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Lignite (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Lignite')</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1517,7 +1548,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Lubricants')</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1552,7 +1583,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Other recovered gases')</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1587,7 +1618,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Non specified own uses\BKB and PB (canonical LEAP sector candidates=['Other loss and own use/Non specified own uses', 'Other loss and own use']; fuel='BKB and PB')</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1622,7 +1653,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Non specified own uses\Crude oil (canonical LEAP sector candidates=['Other loss and own use/Non specified own uses', 'Other loss and own use']; fuel='Crude oil')</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1666,10 +1697,18 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-16.66927599393778</v>
+      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -1677,7 +1716,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1731,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\BKB and PB (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='BKB and PB')</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1727,7 +1766,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Coke oven coke (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Coke oven coke')</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1762,7 +1801,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Gas works gas (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Gas works gas')</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1797,7 +1836,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lignite (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lignite')</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1832,7 +1871,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lubricants')</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1867,7 +1906,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Natural gas liquids')</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1945,7 +1984,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Lignite (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Lignite')</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1980,7 +2019,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Natural gas liquids')</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2058,7 +2097,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Peat (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Peat')</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2093,7 +2132,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Refinery gas not liquefied')</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2124,1890 +2163,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K47"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>enabled</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>branch_path</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>economies_that_need_it</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>economies_resolved_in_templates</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>esto_2024_last_year_signed_pj_all_economies</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>esto_2025_last_year_signed_pj_all_economies</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>esto_2026_last_year_signed_pj_all_economies</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>ninth_reference_average_pj_per_year_all_economies</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>relevance_audit</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>zero filter</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="b">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Demand\All demand aggregated\Other sector\Other recovered gases</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>The sector-split aggregated-demand workflow can produce a small Other sector amount for this fuel, but the economy templates do not expose that branch; the values are immaterial and are intentionally left out. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Other sector\Other recovered gases (sector='Other sector'; 9th sector='Other sector') Relevance audit: 2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12_NZ</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</t>
-        </is>
-      </c>
-      <c r="K2">
-        <f>AND(F2=0,G2=0,H2=0,I2=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="b">
-        <v>0</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Stock Changes\Secondary\Bio jet kerosene</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A small stock-change value can be present in the source data, but the current economy templates do not expose this branch; it is intentionally left out as immaterial. Materiality mapping needs review: Cannot derive source mapping for registry path: Stock Changes\Secondary\Bio jet kerosene Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.042852</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.042873</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K3">
-        <f>AND(F3=0,G3=0,H3=0,I3=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="b">
-        <v>0</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Additives and oxygenates</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Additives and oxygenates (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K4">
-        <f>AND(F4=0,G4=0,H4=0,I4=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="b">
-        <v>0</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
-        <v>-4.809293</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-4.311189828000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K5">
-        <f>AND(F5=0,G5=0,H5=0,I5=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="b">
-        <v>0</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat (sector='Electricity interim'; fuel='Heat'; 9th sector='Electricity interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
-        <v>-1704.741122</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K6">
-        <f>AND(F6=0,G6=0,H6=0,I6=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="b">
-        <v>0</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-3.060635</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-2.743651908</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K7">
-        <f>AND(F7=0,G7=0,H7=0,I7=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="b">
-        <v>0</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" t="n">
-        <v>-0.1022</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-0.102199788</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K8">
-        <f>AND(F8=0,G8=0,H8=0,I8=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Demand\All demand aggregated\Non Energy Use\Blast furnace gas</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Blast furnace gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K9">
-        <f>AND(F9=0,G9=0,H9=0,I9=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Demand\All demand aggregated\Non Energy Use\Gas works gas</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Gas works gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K10">
-        <f>AND(F10=0,G10=0,H10=0,I10=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Demand\All demand aggregated\Non Energy Use\Hydrogen</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Hydrogen (sector='Non Energy Use'; fuel='Hydrogen'; 9th sector='Non Energy Use')</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>01_AUS|05_PRC|10_MAS|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K11">
-        <f>AND(F11=0,G11=0,H11=0,I11=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="b">
-        <v>1</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Demand\All demand aggregated\Non Energy Use\Other recovered gases</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Other recovered gases (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K12">
-        <f>AND(F12=0,G12=0,H12=0,I12=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="b">
-        <v>1</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\Anthracite</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>05_PRC|20_USA</t>
-        </is>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
-        </is>
-      </c>
-      <c r="K13">
-        <f>AND(F13=0,G13=0,H13=0,I13=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="b">
-        <v>1</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\BKB and PB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>01_AUS|05_PRC|16_RUS</t>
-        </is>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>-1.080882</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-1.051718465952</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-4.153502928239663</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K14">
-        <f>AND(F14=0,G14=0,H14=0,I14=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="b">
-        <v>1</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\Blast furnace gas</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.550146</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-4.153502928239663</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K15">
-        <f>AND(F15=0,G15=0,H15=0,I15=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="b">
-        <v>1</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\Lignite</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>05_PRC|12_NZ|16_RUS|20_USA</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-1.096146</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-1.124281404</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K16">
-        <f>AND(F16=0,G16=0,H16=0,I16=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="b">
-        <v>1</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\Lubricants</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K17">
-        <f>AND(F17=0,G17=0,H17=0,I17=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="b">
-        <v>1</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\Other recovered gases</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-4.153502928239663</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K18">
-        <f>AND(F18=0,G18=0,H18=0,I18=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="b">
-        <v>1</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\Patent fuel</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>16_RUS</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-4.153502928239663</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K19">
-        <f>AND(F19=0,G19=0,H19=0,I19=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="b">
-        <v>1</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\Petroleum coke</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.101551</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-2.086408044</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K20">
-        <f>AND(F20=0,G20=0,H20=0,I20=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="b">
-        <v>1</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Coal mines\Refinery gas not liquefied</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K21">
-        <f>AND(F21=0,G21=0,H21=0,I21=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="b">
-        <v>1</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K22">
-        <f>AND(F22=0,G22=0,H22=0,I22=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="b">
-        <v>1</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\BKB and PB</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.499257</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0.48048051744</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K23">
-        <f>AND(F23=0,G23=0,H23=0,I23=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="b">
-        <v>1</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K24">
-        <f>AND(F24=0,G24=0,H24=0,I24=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="b">
-        <v>1</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K25">
-        <f>AND(F25=0,G25=0,H25=0,I25=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="b">
-        <v>1</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coal tar</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F26" t="n">
-        <v>-0.06029</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K26">
-        <f>AND(F26=0,G26=0,H26=0,I26=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="b">
-        <v>1</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K27">
-        <f>AND(F27=0,G27=0,H27=0,I27=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="b">
-        <v>1</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K28">
-        <f>AND(F28=0,G28=0,H28=0,I28=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="b">
-        <v>1</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>01_AUS</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
-        </is>
-      </c>
-      <c r="K29">
-        <f>AND(F29=0,G29=0,H29=0,I29=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="b">
-        <v>1</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lignite</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>05_PRC|16_RUS</t>
-        </is>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K30">
-        <f>AND(F30=0,G30=0,H30=0,I30=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="b">
-        <v>1</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K31">
-        <f>AND(F31=0,G31=0,H31=0,I31=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="b">
-        <v>1</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K32">
-        <f>AND(F32=0,G32=0,H32=0,I32=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="b">
-        <v>1</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Non specified own uses\BKB and PB</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>01_AUS</t>
-        </is>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
-        </is>
-      </c>
-      <c r="K33">
-        <f>AND(F33=0,G33=0,H33=0,I33=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="b">
-        <v>1</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Non specified own uses\Crude oil</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>01_AUS|16_RUS</t>
-        </is>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K34">
-        <f>AND(F34=0,G34=0,H34=0,I34=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="b">
-        <v>1</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Anthracite</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K35">
-        <f>AND(F35=0,G35=0,H35=0,I35=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="b">
-        <v>1</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\BKB and PB</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K36">
-        <f>AND(F36=0,G36=0,H36=0,I36=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="b">
-        <v>1</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Coke oven coke</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K37">
-        <f>AND(F37=0,G37=0,H37=0,I37=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="b">
-        <v>1</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Gas works gas</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K38">
-        <f>AND(F38=0,G38=0,H38=0,I38=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="b">
-        <v>1</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Lignite</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K39">
-        <f>AND(F39=0,G39=0,H39=0,I39=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="b">
-        <v>1</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Lubricants</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F40" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K40">
-        <f>AND(F40=0,G40=0,H40=0,I40=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="b">
-        <v>1</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>01_AUS</t>
-        </is>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
-        </is>
-      </c>
-      <c r="K41">
-        <f>AND(F41=0,G41=0,H41=0,I41=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="b">
-        <v>1</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\BKB and PB</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>05_PRC</t>
-        </is>
-      </c>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-37.58266388971636</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
-        </is>
-      </c>
-      <c r="K42">
-        <f>AND(F42=0,G42=0,H42=0,I42=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="b">
-        <v>1</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Lignite</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>16_RUS</t>
-        </is>
-      </c>
-      <c r="F43" t="n">
-        <v>0</v>
-      </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K43">
-        <f>AND(F43=0,G43=0,H43=0,I43=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="b">
-        <v>1</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>19_THA</t>
-        </is>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
-        </is>
-      </c>
-      <c r="K44">
-        <f>AND(F44=0,G44=0,H44=0,I44=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="b">
-        <v>1</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Other bituminous coal</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>05_PRC|16_RUS</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>-0.133298</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K45">
-        <f>AND(F45=0,G45=0,H45=0,I45=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="b">
-        <v>1</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Peat</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>16_RUS</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K46">
-        <f>AND(F46=0,G46=0,H46=0,I46=0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="b">
-        <v>1</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>16_RUS</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>0</v>
-      </c>
-      <c r="G47" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
-      <c r="K47">
-        <f>AND(F47=0,G47=0,H47=0,I47=0)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -734,10 +734,18 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>43.697275</v>
+      </c>
+      <c r="H10" t="n">
+        <v>127.9521010639872</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -745,7 +753,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -2,17 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet name="branch_exceptions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="README" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'branch_exceptions'!$A$1:$J$47</definedName>
-  </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <definedNames/>
 </workbook>
 </file>
 
@@ -39,18 +33,12 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -58,11 +46,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -322,8 +311,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -336,9 +323,9 @@
   <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="65" customWidth="1" min="2" max="2"/>
-    <col width="32.83203125" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" style="4" min="1" max="1"/>
+    <col width="65" customWidth="1" style="4" min="2" max="2"/>
+    <col width="32.83203125" customWidth="1" style="4" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,28 +426,28 @@
     </row>
     <row r="3">
       <c r="A3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Stock Changes\Secondary\Bio jet kerosene</t>
+          <t>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A small stock-change value can be present in the source data, but the current economy templates do not expose this branch; it is intentionally left out as immaterial. Materiality mapping needs review: Cannot derive source mapping for registry path: Stock Changes\Secondary\Bio jet kerosene Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>-0.042852</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0.042873</v>
+        <v>-4.809293</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-4.311189828000001</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -472,22 +459,22 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>DISABLED — no trigger across audited vintages</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" s="4">
       <c r="A4" t="b">
         <v>0</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Additives and oxygenates</t>
+          <t>Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Additives and oxygenates (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+          <t>Material ESTO evidence is limited to 2023 for 05_PRC (China), at -1704.741122 PJ. This is arguably not a genuine electricity-plant feedstock value because the heat input is better suited to CHP. Retain disabled pending routing confirmation; the 2026 vintage has no material 2024 value.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -496,7 +483,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-1704.741122</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -515,18 +502,18 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="32" customHeight="1" s="4">
       <c r="A5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat</t>
+          <t>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -535,10 +522,10 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.809293</v>
+        <v>-3.060635</v>
       </c>
       <c r="H5" t="n">
-        <v>-4.311189828000001</v>
+        <v>-2.743651908</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -550,22 +537,22 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DISABLED — no trigger across audited vintages</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" s="4">
       <c r="A6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat</t>
+          <t>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat (sector='Electricity interim'; fuel='Heat'; 9th sector='Electricity interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
+          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -574,10 +561,10 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>-1704.741122</v>
+        <v>-0.1022</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.102199788</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -589,85 +576,93 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>DISABLED — no trigger across audited vintages</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="32" customHeight="1" s="4">
       <c r="A7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat</t>
+          <t>Demand\All demand aggregated\Non Energy Use\Blast furnace gas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Blast furnace gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.060635</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.743651908</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1829.600277551402</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DISABLED — no trigger across audited vintages</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
+          <t>CONFIRMED NONZERO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products</t>
+          <t>Demand\All demand aggregated\Non Energy Use\Gas works gas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Gas works gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>05_PRC</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1022</v>
+        <v>43.697275</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.102199788</v>
+        <v>127.9521010639872</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>DISABLED — no trigger across audited vintages</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -677,17 +672,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Demand\All demand aggregated\Non Energy Use\Blast furnace gas</t>
+          <t>Demand\All demand aggregated\Non Energy Use\Hydrogen</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Blast furnace gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Hydrogen (sector='Non Energy Use'; fuel='Hydrogen'; 9th sector='Non Energy Use')</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>01_AUS|05_PRC|10_MAS|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -701,11 +696,11 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>1829.600277551402</v>
+        <v>587.5590317558863</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -720,12 +715,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Demand\All demand aggregated\Non Energy Use\Gas works gas</t>
+          <t>Demand\All demand aggregated\Non Energy Use\Other recovered gases</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Gas works gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Other recovered gases (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -738,13 +733,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>43.697275</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>127.9521010639872</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1829.600277551402</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -763,17 +758,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Demand\All demand aggregated\Non Energy Use\Hydrogen</t>
+          <t>Demand\Other loss and own use\Coal mines\Anthracite</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Hydrogen (sector='Non Energy Use'; fuel='Hydrogen'; 9th sector='Non Energy Use')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>01_AUS|05_PRC|10_MAS|15_PHL|16_RUS|19_THA|20_USA|21_VN</t>
+          <t>05_PRC|20_USA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -787,11 +782,11 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>587.5590317558863</v>
+        <v>-238.4785316762984</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -806,17 +801,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Demand\All demand aggregated\Non Energy Use\Other recovered gases</t>
+          <t>Demand\Other loss and own use\Coal mines\BKB and PB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Other recovered gases (sector='Non Energy Use'; 9th sector='Non Energy Use')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>01_AUS|05_PRC|16_RUS</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -824,17 +819,17 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-1.080882</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-1.051718465952</v>
       </c>
       <c r="I12" t="n">
-        <v>1829.600277551402</v>
+        <v>-4.153502928239663</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -849,22 +844,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\Anthracite</t>
+          <t>Demand\Other loss and own use\Coal mines\Blast furnace gas</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>05_PRC|20_USA</t>
+          <t>05_PRC</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.550146</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -873,11 +868,11 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-238.4785316762984</v>
+        <v>-4.153502928239663</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -892,17 +887,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\BKB and PB</t>
+          <t>Demand\Other loss and own use\Coal mines\Lignite</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>01_AUS|05_PRC|16_RUS</t>
+          <t>05_PRC|12_NZ|16_RUS|20_USA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -910,17 +905,17 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.080882</v>
+        <v>-1.096146</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.051718465952</v>
+        <v>-1.124281404</v>
       </c>
       <c r="I14" t="n">
-        <v>-4.153502928239663</v>
+        <v>0</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -935,12 +930,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\Blast furnace gas</t>
+          <t>Demand\Other loss and own use\Coal mines\Lubricants</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Lubricants')</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -949,18 +944,10 @@
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="n">
-        <v>-0.550146</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-4.153502928239663</v>
-      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -968,7 +955,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>CONFIRMED NONZERO</t>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -978,17 +965,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\Lignite</t>
+          <t>Demand\Other loss and own use\Coal mines\Other recovered gases</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>05_PRC|12_NZ|16_RUS|20_USA</t>
+          <t>05_PRC</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -996,17 +983,17 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.096146</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.124281404</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-4.153502928239663</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1021,32 +1008,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\Lubricants</t>
+          <t>Demand\Other loss and own use\Coal mines\Patent fuel</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Lubricants')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>16_RUS</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-4.153502928239663</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1051,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\Other recovered gases</t>
+          <t>Demand\Other loss and own use\Coal mines\Petroleum coke</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1071,16 +1066,16 @@
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.101551</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-2.086408044</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.153502928239663</v>
+        <v>0</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1099,40 +1094,32 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\Patent fuel</t>
+          <t>Demand\Other loss and own use\Coal mines\Refinery gas not liquefied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Refinery gas not liquefied (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Refinery gas not liquefied')</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16_RUS</t>
+          <t>05_PRC</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-4.153502928239663</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>CONFIRMED NONZERO</t>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1129,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\Petroleum coke</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Anthracite') 2022-vintage check: no material unknown-path finding for 05_PRC. Expected to be unnecessary for the 2026 preliminary vintage; explicitly recheck after the 2026-vintage run before disabling or removing this exception row.</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1156,18 +1143,10 @@
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="n">
-        <v>-0.101551</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-2.086408044</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -1175,7 +1154,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>CONFIRMED NONZERO</t>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1164,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Coal mines\Refinery gas not liquefied</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\BKB and PB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Refinery gas not liquefied (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Refinery gas not liquefied')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1199,10 +1178,18 @@
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-0.499257</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.48048051744</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -1210,7 +1197,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1207,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Anthracite')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Bitumen')</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1255,12 +1242,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\BKB and PB</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Blast furnace gas')</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1269,18 +1256,10 @@
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>-0.499257</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-0.48048051744</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -1288,7 +1267,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>CONFIRMED NONZERO</t>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1277,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coal tar</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Bitumen')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1312,10 +1291,18 @@
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>-0.06029</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
       <c r="J24" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -1323,7 +1310,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1320,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Blast furnace gas')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Coking coal')</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1368,12 +1355,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coal tar</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Gas works gas')</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1382,18 +1369,10 @@
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>-0.06029</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -1401,7 +1380,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>CONFIRMED NONZERO</t>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1411,17 +1390,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Coking coal')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Kerosene type jet fuel')</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>01_AUS</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
@@ -1431,7 +1410,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1446,17 +1425,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lignite</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Gas works gas')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Lignite (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Lignite')</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>05_PRC|16_RUS</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
@@ -1466,7 +1445,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1481,17 +1460,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Kerosene type jet fuel')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Lubricants')</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>01_AUS</t>
+          <t>05_PRC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr"/>
@@ -1501,7 +1480,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -1516,17 +1495,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lignite</t>
+          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Lignite (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Lignite')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Other recovered gases')</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>05_PRC|16_RUS</t>
+          <t>05_PRC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
@@ -1536,7 +1515,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -1551,17 +1530,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants</t>
+          <t>Demand\Other loss and own use\Non specified own uses\BKB and PB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Lubricants')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Non specified own uses\BKB and PB (canonical LEAP sector candidates=['Other loss and own use/Non specified own uses', 'Other loss and own use']; fuel='BKB and PB')</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>01_AUS</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
@@ -1571,7 +1550,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -1586,17 +1565,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases</t>
+          <t>Demand\Other loss and own use\Non specified own uses\Crude oil</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Other recovered gases')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Non specified own uses\Crude oil (canonical LEAP sector candidates=['Other loss and own use/Non specified own uses', 'Other loss and own use']; fuel='Crude oil')</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>01_AUS|16_RUS</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
@@ -1606,7 +1585,7 @@
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -1621,32 +1600,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Non specified own uses\BKB and PB</t>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Anthracite</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Non specified own uses\BKB and PB (canonical LEAP sector candidates=['Other loss and own use/Non specified own uses', 'Other loss and own use']; fuel='BKB and PB')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>01_AUS</t>
+          <t>05_PRC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-16.66927599393778</v>
+      </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -1656,17 +1643,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Non specified own uses\Crude oil</t>
+          <t>Demand\Other loss and own use\Oil and gas extraction\BKB and PB</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Non specified own uses\Crude oil (canonical LEAP sector candidates=['Other loss and own use/Non specified own uses', 'Other loss and own use']; fuel='Crude oil')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\BKB and PB (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='BKB and PB')</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>01_AUS|16_RUS</t>
+          <t>05_PRC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr"/>
@@ -1676,7 +1663,7 @@
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -1691,12 +1678,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Anthracite</t>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Coke oven coke</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Coke oven coke (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Coke oven coke')</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1705,18 +1692,10 @@
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>-16.66927599393778</v>
-      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -1724,7 +1703,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>CONFIRMED NONZERO</t>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1713,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\BKB and PB</t>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Gas works gas</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\BKB and PB (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='BKB and PB')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Gas works gas (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Gas works gas')</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1769,12 +1748,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Coke oven coke</t>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Lignite</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Coke oven coke (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Coke oven coke')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lignite (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lignite')</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1804,12 +1783,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Gas works gas</t>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Lubricants</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Gas works gas (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Gas works gas')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lubricants')</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1839,17 +1818,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Lignite</t>
+          <t>Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lignite (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lignite')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Natural gas liquids')</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>01_AUS</t>
         </is>
       </c>
       <c r="E39" t="inlineStr"/>
@@ -1859,7 +1838,7 @@
       <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -1874,12 +1853,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Lubricants</t>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\BKB and PB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lubricants')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1888,10 +1867,18 @@
         </is>
       </c>
       <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-37.58266388971636</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
       <c r="J40" t="inlineStr">
         <is>
           <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
@@ -1899,7 +1886,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -1909,17 +1896,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids</t>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Lignite</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Natural gas liquids')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Lignite (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Lignite')</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>01_AUS</t>
+          <t>16_RUS</t>
         </is>
       </c>
       <c r="E41" t="inlineStr"/>
@@ -1929,7 +1916,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</t>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -1944,40 +1931,32 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\BKB and PB</t>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Natural gas liquids')</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>05_PRC</t>
+          <t>19_THA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr"/>
-      <c r="F42" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-37.58266388971636</v>
-      </c>
-      <c r="I42" t="n">
-        <v>0</v>
-      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</t>
+          <t>2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>CONFIRMED NONZERO</t>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -1987,32 +1966,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Lignite</t>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Other bituminous coal</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Lignite (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Lignite')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>16_RUS</t>
+          <t>05_PRC|16_RUS</t>
         </is>
       </c>
       <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>-0.133298</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>
@@ -2022,17 +2009,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids</t>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Peat</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Natural gas liquids')</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Peat (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Peat')</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>19_THA</t>
+          <t>16_RUS</t>
         </is>
       </c>
       <c r="E44" t="inlineStr"/>
@@ -2042,7 +2029,7 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</t>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -2057,40 +2044,32 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Other bituminous coal</t>
+          <t>Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Refinery gas not liquefied')</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>05_PRC|16_RUS</t>
+          <t>16_RUS</t>
         </is>
       </c>
       <c r="E45" t="inlineStr"/>
-      <c r="F45" t="n">
-        <v>-0.133298</v>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
+          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>CONFIRMED NONZERO</t>
+          <t>MAPPING INCOMPLETE — seed triggered</t>
         </is>
       </c>
     </row>
@@ -2100,17 +2079,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Peat</t>
+          <t>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Petroleum coke</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Peat (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Peat')</t>
+          <t>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Petroleum coke (canonical LEAP sector candidates=['CHP interim/Processes/CHP interim/Feedstock Fuels', 'CHP interim/Processes/CHP interim', 'CHP interim/Processes', 'CHP interim']; fuel='Petroleum coke')</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>16_RUS</t>
+          <t>20_USA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr"/>
@@ -2118,14 +2097,10 @@
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>MAPPING INCOMPLETE — source mapping required</t>
         </is>
       </c>
     </row>
@@ -2135,17 +2110,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied</t>
+          <t>Demand\All demand aggregated\Black liquor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Refinery gas not liquefied')</t>
+          <t>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Black liquor (canonical LEAP sector candidates=['All demand aggregated']; fuel='Black liquor')</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>16_RUS</t>
+          <t>20_USA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr"/>
@@ -2153,19 +2128,14 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</t>
-        </is>
-      </c>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>MAPPING INCOMPLETE — seed triggered</t>
+          <t>MAPPING INCOMPLETE — source mapping required</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J47"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2179,8 +2149,8 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="110" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" style="4" min="1" max="1"/>
+    <col width="110" customWidth="1" style="4" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2219,7 +2189,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="28" customHeight="1" s="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>Use</t>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -320,7 +320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14"/>
   <cols>
     <col width="12" customWidth="1" style="4" min="1" max="1"/>
@@ -2132,6 +2132,76 @@
       <c r="K47" t="inlineStr">
         <is>
           <t>MAPPING INCOMPLETE — source mapping required</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="b">
+        <v>1</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Resources\Primary\Unknown</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Materiality mapping needs review: Cannot derive source mapping for registry path: Resources\Primary\Unknown</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20_USA</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>MAPPING INCOMPLETE — source mapping required</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="b">
+        <v>1</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Demand\All demand aggregated\Industry\Geothermal</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20_USA</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="n">
+        <v>4.512571</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.695957</v>
+      </c>
+      <c r="H49" t="n">
+        <v>4.623399352000001</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>CONFIRMED NONZERO</t>
         </is>
       </c>
     </row>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="Rca8d12aa44de48c7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="R989ffffe464a4349"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="R4b90f01d978044eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="R64c1ff976b1047c4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3007,6 +3007,106 @@
         <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>Transformation\Non specified transformation\Output Fuels\Additives and oxygenates</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists.</x:v>
+      </x:c>
+      <x:c r="D54" t="str">
+        <x:v>02_BD|20_USA</x:v>
+      </x:c>
+      <x:c r="E54" t="str"/>
+      <x:c r="F54" t="str"/>
+      <x:c r="G54" t="str"/>
+      <x:c r="H54" t="str"/>
+      <x:c r="I54" t="str"/>
+      <x:c r="J54" t="str">
+        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
+      </x:c>
+      <x:c r="K54" t="str">
+        <x:v>EXCEPTION REQUESTED — reviewed missing branch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>Transformation\Non specified transformation\Output Fuels\Refinery feedstocks</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists.</x:v>
+      </x:c>
+      <x:c r="D55" t="str">
+        <x:v>02_BD|20_USA</x:v>
+      </x:c>
+      <x:c r="E55" t="str"/>
+      <x:c r="F55" t="str"/>
+      <x:c r="G55" t="str"/>
+      <x:c r="H55" t="str"/>
+      <x:c r="I55" t="str"/>
+      <x:c r="J55" t="str">
+        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
+      </x:c>
+      <x:c r="K55" t="str">
+        <x:v>EXCEPTION REQUESTED — reviewed missing branch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>Transformation\Coke ovens\Processes\Coke ovens\Feedstock Fuels\Coke oven coke</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero/coverage transformation rows for 11_MEX, but the selected Mexico template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists.</x:v>
+      </x:c>
+      <x:c r="D56" t="str">
+        <x:v>11_MEX</x:v>
+      </x:c>
+      <x:c r="E56" t="str"/>
+      <x:c r="F56" t="str"/>
+      <x:c r="G56" t="str"/>
+      <x:c r="H56" t="str"/>
+      <x:c r="I56" t="str"/>
+      <x:c r="J56" t="str">
+        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
+      </x:c>
+      <x:c r="K56" t="str">
+        <x:v>EXCEPTION REQUESTED — reviewed missing branch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="5" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>Transformation\Transfers unallocated\Output Fuels\Natural gas liquids</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated transfer rows for 19_THA, but the selected Thailand template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists.</x:v>
+      </x:c>
+      <x:c r="D57" t="str">
+        <x:v>19_THA</x:v>
+      </x:c>
+      <x:c r="E57" t="str"/>
+      <x:c r="F57" t="str"/>
+      <x:c r="G57" t="str"/>
+      <x:c r="H57" t="str"/>
+      <x:c r="I57" t="str"/>
+      <x:c r="J57" t="str">
+        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
+      </x:c>
+      <x:c r="K57" t="str">
+        <x:v>EXCEPTION REQUESTED — reviewed missing branch</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="R1873a3658fd94806"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="R0feef526c8f44a8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="Re44c639666914d57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Re688c3c3592e4dfe"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1258,7 +1258,7 @@
         <x:v>Demand\Other loss and own use\Oil and gas extraction\BKB and PB</x:v>
       </x:c>
       <x:c r="C32" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\BKB and PB (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='BKB and PB') Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="D32" t="str"/>
       <x:c r="E32"/>
@@ -1289,7 +1289,7 @@
         <x:v>Demand\Other loss and own use\Oil and gas extraction\Coke oven coke</x:v>
       </x:c>
       <x:c r="C33" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Coke oven coke (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Coke oven coke') Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="D33" t="str"/>
       <x:c r="E33"/>
@@ -1320,7 +1320,7 @@
         <x:v>Demand\Other loss and own use\Oil and gas extraction\Gas works gas</x:v>
       </x:c>
       <x:c r="C34" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Gas works gas (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Gas works gas') Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="D34" t="str"/>
       <x:c r="E34"/>
@@ -1351,7 +1351,7 @@
         <x:v>Demand\Other loss and own use\Oil and gas extraction\Lignite</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lignite (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lignite') Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="D35" t="str"/>
       <x:c r="E35"/>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="Re44c639666914d57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Re688c3c3592e4dfe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="R843b68bb88c445b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Rd24aa858a93a47d3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -387,22 +387,30 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" t="str">
-        <x:v>Demand\All demand aggregated\Black liquor</x:v>
+        <x:v>Demand\All demand aggregated\Industry\Geothermal</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Black liquor (canonical LEAP sector candidates=['All demand aggregated']; fuel='Black liquor')</x:v>
+        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate.</x:v>
       </x:c>
       <x:c r="D2" t="str">
         <x:v>20_USA</x:v>
       </x:c>
       <x:c r="E2"/>
-      <x:c r="F2"/>
-      <x:c r="G2"/>
-      <x:c r="H2"/>
-      <x:c r="I2"/>
+      <x:c r="F2" t="str">
+        <x:v>4.512571</x:v>
+      </x:c>
+      <x:c r="G2" t="str">
+        <x:v>4.695957</x:v>
+      </x:c>
+      <x:c r="H2" t="str">
+        <x:v>4.623399352000001</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J2"/>
       <x:c r="K2" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -410,28 +418,30 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" t="str">
-        <x:v>Demand\All demand aggregated\Industry\Geothermal</x:v>
+        <x:v>Demand\All demand aggregated\Non Energy Use\Blast furnace gas</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Blast furnace gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
       </x:c>
       <x:c r="D3" t="str">
-        <x:v>20_USA</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E3"/>
-      <x:c r="F3" t="n">
-        <x:v>4.512571</x:v>
-      </x:c>
-      <x:c r="G3" t="n">
-        <x:v>4.695957</x:v>
-      </x:c>
-      <x:c r="H3" t="n">
-        <x:v>4.623399352000001</x:v>
-      </x:c>
-      <x:c r="I3" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J3"/>
+      <x:c r="F3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H3" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>1829.600277551402</x:v>
+      </x:c>
+      <x:c r="J3" t="str">
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+      </x:c>
       <x:c r="K3" t="str">
         <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
@@ -441,26 +451,26 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>Demand\All demand aggregated\Non Energy Use\Blast furnace gas</x:v>
+        <x:v>Demand\All demand aggregated\Non Energy Use\Gas works gas</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Blast furnace gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Gas works gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E4"/>
-      <x:c r="F4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H4" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I4" t="n">
-        <x:v>1829.600277551402</x:v>
+      <x:c r="F4" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G4" t="str">
+        <x:v>43.697275</x:v>
+      </x:c>
+      <x:c r="H4" t="str">
+        <x:v>127.9521010639872</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J4" t="str">
         <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
@@ -474,29 +484,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B5" t="str">
-        <x:v>Demand\All demand aggregated\Non Energy Use\Gas works gas</x:v>
+        <x:v>Demand\All demand aggregated\Non Energy Use\Hydrogen</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Gas works gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Hydrogen (sector='Non Energy Use'; fuel='Hydrogen'; 9th sector='Non Energy Use')</x:v>
       </x:c>
       <x:c r="D5" t="str">
-        <x:v>05_PRC</x:v>
+        <x:v>01_AUS|05_PRC|10_MAS|15_PHL|16_RUS|19_THA|20_USA|21_VN</x:v>
       </x:c>
       <x:c r="E5"/>
-      <x:c r="F5" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" t="n">
-        <x:v>43.697275</x:v>
-      </x:c>
-      <x:c r="H5" t="n">
-        <x:v>127.9521010639872</x:v>
-      </x:c>
-      <x:c r="I5" t="n">
-        <x:v>0</x:v>
+      <x:c r="F5" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G5" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H5" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>587.5590317558863</x:v>
       </x:c>
       <x:c r="J5" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="K5" t="str">
         <x:v>CONFIRMED NONZERO</x:v>
@@ -507,29 +517,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" t="str">
-        <x:v>Demand\All demand aggregated\Non Energy Use\Hydrogen</x:v>
+        <x:v>Demand\All demand aggregated\Non Energy Use\Other recovered gases</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Hydrogen (sector='Non Energy Use'; fuel='Hydrogen'; 9th sector='Non Energy Use')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Other recovered gases (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
       </x:c>
       <x:c r="D6" t="str">
-        <x:v>01_AUS|05_PRC|10_MAS|15_PHL|16_RUS|19_THA|20_USA|21_VN</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E6"/>
-      <x:c r="F6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H6" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I6" t="n">
-        <x:v>587.5590317558863</x:v>
+      <x:c r="F6" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>1829.600277551402</x:v>
       </x:c>
       <x:c r="J6" t="str">
-        <x:v>2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K6" t="str">
         <x:v>CONFIRMED NONZERO</x:v>
@@ -537,18 +547,18 @@
     </x:row>
     <x:row r="7" s="3" customFormat="1" ht="21.399999618530273" customHeight="1">
       <x:c r="A7" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B7" t="str">
-        <x:v>Demand\All demand aggregated\Non Energy Use\Other recovered gases</x:v>
+        <x:v>Demand\All demand aggregated\Other sector\Other recovered gases</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Other recovered gases (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
-      </x:c>
-      <x:c r="D7" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
-      <x:c r="E7"/>
+        <x:v>The sector-split aggregated-demand workflow can produce a small Other sector amount for this fuel, but the economy templates do not expose that branch; the values are immaterial and are intentionally left out. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D7" t="str"/>
+      <x:c r="E7" t="str">
+        <x:v>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</x:v>
+      </x:c>
       <x:c r="F7" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -559,13 +569,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I7" t="n">
-        <x:v>1829.600277551402</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J7" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K7" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -573,26 +583,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B8" t="str">
-        <x:v>Demand\All demand aggregated\Other sector\Other recovered gases</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\Anthracite</x:v>
       </x:c>
       <x:c r="C8" t="str">
-        <x:v>The sector-split aggregated-demand workflow can produce a small Other sector amount for this fuel, but the economy templates do not expose that branch; the values are immaterial and are intentionally left out. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Other sector\Other recovered gases (sector='Other sector'; 9th sector='Other sector') Relevance audit: 2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</x:v>
       </x:c>
       <x:c r="D8" t="str">
-        <x:v>12_NZ</x:v>
-      </x:c>
-      <x:c r="E8" t="str">
-        <x:v>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</x:v>
-      </x:c>
-      <x:c r="F8"/>
-      <x:c r="G8"/>
-      <x:c r="H8"/>
-      <x:c r="I8"/>
+        <x:v>05_PRC|20_USA</x:v>
+      </x:c>
+      <x:c r="E8"/>
+      <x:c r="F8" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>-238.4785316762984</x:v>
+      </x:c>
       <x:c r="J8" t="str">
-        <x:v>2022 base final stage: triggered for 01_AUS|02_BD|10_MAS|11_MEX|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 12_NZ (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|19_THA|20_USA|21_VN.</x:v>
+        <x:v>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</x:v>
       </x:c>
       <x:c r="K8" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -600,29 +616,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B9" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\Anthracite</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\BKB and PB</x:v>
       </x:c>
       <x:c r="C9" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="D9" t="str">
-        <x:v>05_PRC|20_USA</x:v>
+        <x:v>01_AUS|05_PRC|16_RUS</x:v>
       </x:c>
       <x:c r="E9"/>
-      <x:c r="F9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" t="n">
-        <x:v>-238.4785316762984</x:v>
+      <x:c r="F9" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>-1.080882</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>-1.051718465952</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>-4.153502928239663</x:v>
       </x:c>
       <x:c r="J9" t="str">
-        <x:v>2022 base final stage: triggered for 20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|20_USA.</x:v>
+        <x:v>2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="K9" t="str">
         <x:v>CONFIRMED NONZERO</x:v>
@@ -633,29 +649,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B10" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\BKB and PB</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\Blast furnace gas</x:v>
       </x:c>
       <x:c r="C10" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D10" t="str">
-        <x:v>01_AUS|05_PRC|16_RUS</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E10"/>
-      <x:c r="F10" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" t="n">
-        <x:v>-1.080882</x:v>
-      </x:c>
-      <x:c r="H10" t="n">
-        <x:v>-1.051718465952</x:v>
-      </x:c>
-      <x:c r="I10" t="n">
+      <x:c r="F10" t="str">
+        <x:v>-0.550146</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
         <x:v>-4.153502928239663</x:v>
       </x:c>
       <x:c r="J10" t="str">
-        <x:v>2022 base final stage: triggered for 01_AUS|16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K10" t="str">
         <x:v>CONFIRMED NONZERO</x:v>
@@ -666,29 +682,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B11" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\Blast furnace gas</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\Lignite</x:v>
       </x:c>
       <x:c r="C11" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="D11" t="str">
-        <x:v>05_PRC</x:v>
+        <x:v>05_PRC|12_NZ|16_RUS|20_USA</x:v>
       </x:c>
       <x:c r="E11"/>
-      <x:c r="F11" t="n">
-        <x:v>-0.550146</x:v>
-      </x:c>
-      <x:c r="G11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I11" t="n">
-        <x:v>-4.153502928239663</x:v>
+      <x:c r="F11" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>-1.096146</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>-1.124281404</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J11" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="K11" t="str">
         <x:v>CONFIRMED NONZERO</x:v>
@@ -699,32 +715,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B12" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\Lignite</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\Lubricants</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Lubricants')</x:v>
       </x:c>
       <x:c r="D12" t="str">
-        <x:v>05_PRC|12_NZ|16_RUS|20_USA</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E12"/>
-      <x:c r="F12" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" t="n">
-        <x:v>-1.096146</x:v>
-      </x:c>
-      <x:c r="H12" t="n">
-        <x:v>-1.124281404</x:v>
-      </x:c>
-      <x:c r="I12" t="n">
-        <x:v>0</x:v>
+      <x:c r="F12" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G12" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H12" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>-0.21924697168265594</x:v>
       </x:c>
       <x:c r="J12" t="str">
-        <x:v>2022 base final stage: triggered for 12_NZ|16_RUS|20_USA. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC|12_NZ|20_USA. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -732,24 +748,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B13" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\Lubricants</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\Other recovered gases</x:v>
       </x:c>
       <x:c r="C13" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Lubricants')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D13" t="str">
         <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E13"/>
-      <x:c r="F13"/>
-      <x:c r="G13"/>
-      <x:c r="H13"/>
-      <x:c r="I13"/>
+      <x:c r="F13" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H13" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>-4.153502928239663</x:v>
+      </x:c>
       <x:c r="J13" t="str">
         <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -757,29 +781,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B14" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\Other recovered gases</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\Patent fuel</x:v>
       </x:c>
       <x:c r="C14" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="D14" t="str">
-        <x:v>05_PRC</x:v>
+        <x:v>16_RUS</x:v>
       </x:c>
       <x:c r="E14"/>
-      <x:c r="F14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H14" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I14" t="n">
+      <x:c r="F14" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H14" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
         <x:v>-4.153502928239663</x:v>
       </x:c>
       <x:c r="J14" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="K14" t="str">
         <x:v>CONFIRMED NONZERO</x:v>
@@ -790,29 +814,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B15" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\Patent fuel</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\Petroleum coke</x:v>
       </x:c>
       <x:c r="C15" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D15" t="str">
-        <x:v>16_RUS</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E15"/>
-      <x:c r="F15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H15" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I15" t="n">
-        <x:v>-4.153502928239663</x:v>
+      <x:c r="F15" t="str">
+        <x:v>-0.101551</x:v>
+      </x:c>
+      <x:c r="G15" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H15" t="str">
+        <x:v>-2.086408044</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J15" t="str">
-        <x:v>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K15" t="str">
         <x:v>CONFIRMED NONZERO</x:v>
@@ -820,85 +844,95 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B16" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\Petroleum coke</x:v>
+        <x:v>Demand\Other loss and own use\Coal mines\Refinery gas not liquefied</x:v>
       </x:c>
       <x:c r="C16" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
-      </x:c>
-      <x:c r="D16" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D16" t="str"/>
       <x:c r="E16"/>
       <x:c r="F16" t="n">
-        <x:v>-0.101551</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="H16" t="n">
-        <x:v>-2.086408044</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I16" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J16" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K16" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B17" t="str">
-        <x:v>Demand\Other loss and own use\Coal mines\Refinery gas not liquefied</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite</x:v>
       </x:c>
       <x:c r="C17" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Refinery gas not liquefied (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Refinery gas not liquefied')</x:v>
-      </x:c>
-      <x:c r="D17" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D17" t="str"/>
       <x:c r="E17"/>
-      <x:c r="F17"/>
-      <x:c r="G17"/>
-      <x:c r="H17"/>
-      <x:c r="I17"/>
+      <x:c r="F17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I17" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J17" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K17" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B18" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen</x:v>
       </x:c>
       <x:c r="C18" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Anthracite (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Anthracite') 2022-vintage check: no material unknown-path finding for 05_PRC. Expected to be unnecessary for the 2026 preliminary vintage; explicitly recheck after the 2026-vintage run before disabling or removing this exception row.</x:v>
-      </x:c>
-      <x:c r="D18" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D18" t="str"/>
       <x:c r="E18"/>
-      <x:c r="F18"/>
-      <x:c r="G18"/>
-      <x:c r="H18"/>
-      <x:c r="I18"/>
+      <x:c r="F18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I18" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J18" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K18" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -906,57 +940,63 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B19" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\BKB and PB</x:v>
       </x:c>
       <x:c r="C19" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Bitumen (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Bitumen')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D19" t="str">
         <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E19"/>
-      <x:c r="F19"/>
-      <x:c r="G19"/>
-      <x:c r="H19"/>
-      <x:c r="I19"/>
+      <x:c r="F19" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" t="str">
+        <x:v>-0.499257</x:v>
+      </x:c>
+      <x:c r="H19" t="str">
+        <x:v>-0.48048051744</x:v>
+      </x:c>
+      <x:c r="I19" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J19" t="str">
         <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K19" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B20" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\BKB and PB</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas</x:v>
       </x:c>
       <x:c r="C20" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
-      </x:c>
-      <x:c r="D20" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D20" t="str"/>
       <x:c r="E20"/>
       <x:c r="F20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G20" t="n">
-        <x:v>-0.499257</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H20" t="n">
-        <x:v>-0.48048051744</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I20" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J20" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -964,42 +1004,48 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B21" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Coal tar</x:v>
       </x:c>
       <x:c r="C21" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Blast furnace gas (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Blast furnace gas')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D21" t="str">
         <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E21"/>
-      <x:c r="F21"/>
-      <x:c r="G21"/>
-      <x:c r="H21"/>
-      <x:c r="I21"/>
+      <x:c r="F21" t="str">
+        <x:v>-0.06029</x:v>
+      </x:c>
+      <x:c r="G21" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I21" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J21" t="str">
         <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K21" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B22" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Coal tar</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal</x:v>
       </x:c>
       <x:c r="C22" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
-      </x:c>
-      <x:c r="D22" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D22" t="str"/>
       <x:c r="E22"/>
       <x:c r="F22" t="n">
-        <x:v>-0.06029</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G22" t="n">
         <x:v>0</x:v>
@@ -1011,185 +1057,227 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J22" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K22" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B23" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas</x:v>
       </x:c>
       <x:c r="C23" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Coking coal (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Coking coal')</x:v>
-      </x:c>
-      <x:c r="D23" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D23" t="str"/>
       <x:c r="E23"/>
-      <x:c r="F23"/>
-      <x:c r="G23"/>
-      <x:c r="H23"/>
-      <x:c r="I23"/>
+      <x:c r="F23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I23" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J23" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K23" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B24" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel</x:v>
       </x:c>
       <x:c r="C24" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Gas works gas (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Gas works gas')</x:v>
-      </x:c>
-      <x:c r="D24" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D24" t="str"/>
       <x:c r="E24"/>
-      <x:c r="F24"/>
-      <x:c r="G24"/>
-      <x:c r="H24"/>
-      <x:c r="I24"/>
+      <x:c r="F24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I24" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J24" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K24" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B25" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Lignite</x:v>
       </x:c>
       <x:c r="C25" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Kerosene type jet fuel (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Kerosene type jet fuel')</x:v>
-      </x:c>
-      <x:c r="D25" t="str">
-        <x:v>01_AUS</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D25" t="str"/>
       <x:c r="E25"/>
-      <x:c r="F25"/>
-      <x:c r="G25"/>
-      <x:c r="H25"/>
-      <x:c r="I25"/>
+      <x:c r="F25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I25" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J25" t="str">
-        <x:v>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</x:v>
+        <x:v>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K25" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B26" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Lignite</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants</x:v>
       </x:c>
       <x:c r="C26" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Lignite (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Lignite')</x:v>
-      </x:c>
-      <x:c r="D26" t="str">
-        <x:v>05_PRC|16_RUS</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D26" t="str"/>
       <x:c r="E26"/>
-      <x:c r="F26"/>
-      <x:c r="G26"/>
-      <x:c r="H26"/>
-      <x:c r="I26"/>
+      <x:c r="F26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I26" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J26" t="str">
-        <x:v>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K26" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B27" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants</x:v>
+        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases</x:v>
       </x:c>
       <x:c r="C27" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Lubricants')</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D27" t="str"/>
       <x:c r="E27"/>
-      <x:c r="F27"/>
-      <x:c r="G27"/>
-      <x:c r="H27"/>
-      <x:c r="I27"/>
+      <x:c r="F27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J27" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K27" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B28" t="str">
-        <x:v>Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases</x:v>
+        <x:v>Demand\Other loss and own use\Non specified own uses\BKB and PB</x:v>
       </x:c>
       <x:c r="C28" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Electricity CHP and heat plants\Other recovered gases (canonical LEAP sector candidates=['Other loss and own use/Electricity CHP and heat plants', 'Other loss and own use']; fuel='Other recovered gases')</x:v>
-      </x:c>
-      <x:c r="D28" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D28" t="str"/>
       <x:c r="E28"/>
-      <x:c r="F28"/>
-      <x:c r="G28"/>
-      <x:c r="H28"/>
-      <x:c r="I28"/>
+      <x:c r="F28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I28" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J28" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K28" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B29" t="str">
-        <x:v>Demand\Other loss and own use\Non specified own uses\BKB and PB</x:v>
+        <x:v>Demand\Other loss and own use\Non specified own uses\Crude oil</x:v>
       </x:c>
       <x:c r="C29" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Non specified own uses\BKB and PB (canonical LEAP sector candidates=['Other loss and own use/Non specified own uses', 'Other loss and own use']; fuel='BKB and PB')</x:v>
-      </x:c>
-      <x:c r="D29" t="str">
-        <x:v>01_AUS</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D29" t="str"/>
       <x:c r="E29"/>
-      <x:c r="F29"/>
-      <x:c r="G29"/>
-      <x:c r="H29"/>
-      <x:c r="I29"/>
+      <x:c r="F29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I29" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J29" t="str">
-        <x:v>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</x:v>
+        <x:v>2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K29" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -1197,39 +1285,45 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B30" t="str">
-        <x:v>Demand\Other loss and own use\Non specified own uses\Crude oil</x:v>
+        <x:v>Demand\Other loss and own use\Oil and gas extraction\Anthracite</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Non specified own uses\Crude oil (canonical LEAP sector candidates=['Other loss and own use/Non specified own uses', 'Other loss and own use']; fuel='Crude oil')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D30" t="str">
-        <x:v>01_AUS|16_RUS</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="G30"/>
-      <x:c r="H30"/>
-      <x:c r="I30"/>
+      <x:c r="F30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H30" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I30" t="str">
+        <x:v>-16.66927599393778</x:v>
+      </x:c>
       <x:c r="J30" t="str">
-        <x:v>2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K30" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B31" t="str">
-        <x:v>Demand\Other loss and own use\Oil and gas extraction\Anthracite</x:v>
+        <x:v>Demand\Other loss and own use\Oil and gas extraction\BKB and PB</x:v>
       </x:c>
       <x:c r="C31" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
-      </x:c>
-      <x:c r="D31" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D31"/>
       <x:c r="E31"/>
       <x:c r="F31" t="n">
         <x:v>0</x:v>
@@ -1241,13 +1335,13 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I31" t="n">
-        <x:v>-16.66927599393778</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J31" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K31" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>DISABLED — direct source zero; proxy producer fix required</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -1255,12 +1349,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B32" t="str">
-        <x:v>Demand\Other loss and own use\Oil and gas extraction\BKB and PB</x:v>
+        <x:v>Demand\Other loss and own use\Oil and gas extraction\Coke oven coke</x:v>
       </x:c>
       <x:c r="C32" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D32" t="str"/>
+      <x:c r="D32"/>
       <x:c r="E32"/>
       <x:c r="F32" t="n">
         <x:v>0</x:v>
@@ -1286,12 +1380,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B33" t="str">
-        <x:v>Demand\Other loss and own use\Oil and gas extraction\Coke oven coke</x:v>
+        <x:v>Demand\Other loss and own use\Oil and gas extraction\Gas works gas</x:v>
       </x:c>
       <x:c r="C33" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D33" t="str"/>
+      <x:c r="D33"/>
       <x:c r="E33"/>
       <x:c r="F33" t="n">
         <x:v>0</x:v>
@@ -1317,12 +1411,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B34" t="str">
-        <x:v>Demand\Other loss and own use\Oil and gas extraction\Gas works gas</x:v>
+        <x:v>Demand\Other loss and own use\Oil and gas extraction\Lignite</x:v>
       </x:c>
       <x:c r="C34" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D34" t="str"/>
+      <x:c r="D34"/>
       <x:c r="E34"/>
       <x:c r="F34" t="n">
         <x:v>0</x:v>
@@ -1345,58 +1439,66 @@
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="4" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B35" t="str">
-        <x:v>Demand\Other loss and own use\Oil and gas extraction\Lignite</x:v>
+        <x:v>Demand\Other loss and own use\Oil and gas extraction\Lubricants</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
-      </x:c>
-      <x:c r="D35" t="str"/>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lubricants')</x:v>
+      </x:c>
+      <x:c r="D35" t="str">
+        <x:v>05_PRC</x:v>
+      </x:c>
       <x:c r="E35"/>
-      <x:c r="F35" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H35" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I35" t="n">
-        <x:v>0</x:v>
+      <x:c r="F35" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G35" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H35" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I35" t="str">
+        <x:v>-145.0502877281209</x:v>
       </x:c>
       <x:c r="J35" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: PRC ESTO 10.01.12 Oil and gas extraction is zero for this fuel in 2022–2024, and the corresponding Ninth 10_01_12 projection is zero or absent. The prior nonzero seed row is a proxy-producer defect, not a missing LEAP template branch.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>DISABLED — direct source zero; proxy producer fix required</x:v>
+        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B36" t="str">
-        <x:v>Demand\Other loss and own use\Oil and gas extraction\Lubricants</x:v>
+        <x:v>Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids</x:v>
       </x:c>
       <x:c r="C36" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lubricants')</x:v>
-      </x:c>
-      <x:c r="D36" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D36" t="str"/>
       <x:c r="E36"/>
-      <x:c r="F36"/>
-      <x:c r="G36"/>
-      <x:c r="H36"/>
-      <x:c r="I36"/>
+      <x:c r="F36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I36" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J36" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K36" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -1404,39 +1506,45 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B37" t="str">
-        <x:v>Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids</x:v>
+        <x:v>Demand\Other loss and own use\Transmission and distribution loss\BKB and PB</x:v>
       </x:c>
       <x:c r="C37" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Natural gas liquids (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Natural gas liquids')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D37" t="str">
-        <x:v>01_AUS</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E37"/>
-      <x:c r="F37"/>
-      <x:c r="G37"/>
-      <x:c r="H37"/>
-      <x:c r="I37"/>
+      <x:c r="F37" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G37" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37" t="str">
+        <x:v>-37.58266388971636</x:v>
+      </x:c>
+      <x:c r="I37" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J37" t="str">
-        <x:v>2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS.</x:v>
+        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K37" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B38" t="str">
-        <x:v>Demand\Other loss and own use\Transmission and distribution loss\BKB and PB</x:v>
+        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Lignite</x:v>
       </x:c>
       <x:c r="C38" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
-      </x:c>
-      <x:c r="D38" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D38" t="str"/>
       <x:c r="E38"/>
       <x:c r="F38" t="n">
         <x:v>0</x:v>
@@ -1445,41 +1553,47 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H38" t="n">
-        <x:v>-37.58266388971636</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I38" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J38" t="str">
-        <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
+        <x:v>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K38" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B39" t="str">
-        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Lignite</x:v>
+        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids</x:v>
       </x:c>
       <x:c r="C39" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Lignite (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Lignite')</x:v>
-      </x:c>
-      <x:c r="D39" t="str">
-        <x:v>16_RUS</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D39" t="str"/>
       <x:c r="E39"/>
-      <x:c r="F39"/>
-      <x:c r="G39"/>
-      <x:c r="H39"/>
-      <x:c r="I39"/>
+      <x:c r="F39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I39" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J39" t="str">
-        <x:v>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K39" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -1487,42 +1601,48 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B40" t="str">
-        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids</x:v>
+        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Other bituminous coal</x:v>
       </x:c>
       <x:c r="C40" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Natural gas liquids (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Natural gas liquids')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="D40" t="str">
-        <x:v>19_THA</x:v>
+        <x:v>05_PRC|16_RUS</x:v>
       </x:c>
       <x:c r="E40"/>
-      <x:c r="F40"/>
-      <x:c r="G40"/>
-      <x:c r="H40"/>
-      <x:c r="I40"/>
+      <x:c r="F40" t="str">
+        <x:v>-0.133298</x:v>
+      </x:c>
+      <x:c r="G40" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H40" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I40" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J40" t="str">
-        <x:v>2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA.</x:v>
+        <x:v>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="K40" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B41" t="str">
-        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Other bituminous coal</x:v>
+        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Peat</x:v>
       </x:c>
       <x:c r="C41" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
-      </x:c>
-      <x:c r="D41" t="str">
-        <x:v>05_PRC|16_RUS</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D41" t="str"/>
       <x:c r="E41"/>
       <x:c r="F41" t="n">
-        <x:v>-0.133298</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G41" t="n">
         <x:v>0</x:v>
@@ -1534,35 +1654,41 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="J41" t="str">
-        <x:v>2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K41" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B42" t="str">
-        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Peat</x:v>
+        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied</x:v>
       </x:c>
       <x:c r="C42" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Peat (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Peat')</x:v>
-      </x:c>
-      <x:c r="D42" t="str">
-        <x:v>16_RUS</x:v>
-      </x:c>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
+      </x:c>
+      <x:c r="D42" t="str"/>
       <x:c r="E42"/>
-      <x:c r="F42"/>
-      <x:c r="G42"/>
-      <x:c r="H42"/>
-      <x:c r="I42"/>
+      <x:c r="F42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I42" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J42" t="str">
-        <x:v>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
       <x:c r="K42" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>DISABLED — stale; current producer emits zero</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -1570,47 +1696,61 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B43" t="str">
-        <x:v>Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied</x:v>
+        <x:v>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Transmission and distribution loss\Refinery gas not liquefied (canonical LEAP sector candidates=['Other loss and own use/Transmission and distribution loss', 'Other loss and own use']; fuel='Refinery gas not liquefied')</x:v>
-      </x:c>
-      <x:c r="D43" t="str">
-        <x:v>16_RUS</x:v>
-      </x:c>
+        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
+      </x:c>
+      <x:c r="D43"/>
       <x:c r="E43"/>
-      <x:c r="F43"/>
-      <x:c r="G43"/>
-      <x:c r="H43"/>
-      <x:c r="I43"/>
+      <x:c r="F43" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G43" t="str">
+        <x:v>-4.809293</x:v>
+      </x:c>
+      <x:c r="H43" t="str">
+        <x:v>-4.311189828000001</x:v>
+      </x:c>
+      <x:c r="I43" t="str">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J43" t="str">
-        <x:v>2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
+        <x:v>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="K43" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B44" t="str">
-        <x:v>Resources\Primary\Unknown</x:v>
+        <x:v>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Petroleum coke</x:v>
       </x:c>
       <x:c r="C44" t="str">
-        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Materiality mapping needs review: Cannot derive source mapping for registry path: Resources\Primary\Unknown</x:v>
-      </x:c>
-      <x:c r="D44" t="str">
-        <x:v>20_USA</x:v>
-      </x:c>
+        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
+      </x:c>
+      <x:c r="D44" t="str"/>
       <x:c r="E44"/>
-      <x:c r="F44"/>
-      <x:c r="G44"/>
-      <x:c r="H44"/>
-      <x:c r="I44"/>
-      <x:c r="J44"/>
+      <x:c r="F44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J44" t="str">
+        <x:v>Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
+      </x:c>
       <x:c r="K44" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>DISABLED — zero across maintained sources</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -1618,109 +1758,125 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B45" t="str">
-        <x:v>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat</x:v>
+        <x:v>Transformation\Coke ovens\Processes\Coke ovens\Feedstock Fuels\Coke oven coke</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
-      </x:c>
-      <x:c r="D45"/>
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero/coverage transformation rows for 11_MEX, but the selected Mexico template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Coke ovens\Processes\Coke ovens\Feedstock Fuels\Coke oven coke (canonical LEAP sector candidates=['Coke ovens/Processes/Coke ovens/Feedstock Fuels', 'Coke ovens/Processes/Coke ovens', 'Coke ovens/Processes', 'Coke ovens']; fuel='Coke oven coke')</x:v>
+      </x:c>
+      <x:c r="D45" t="str">
+        <x:v>11_MEX</x:v>
+      </x:c>
       <x:c r="E45"/>
-      <x:c r="F45" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G45" t="n">
-        <x:v>-4.809293</x:v>
-      </x:c>
-      <x:c r="H45" t="n">
-        <x:v>-4.311189828000001</x:v>
-      </x:c>
-      <x:c r="I45" t="n">
-        <x:v>0</x:v>
+      <x:c r="F45" t="str">
+        <x:v>16425.159078</x:v>
+      </x:c>
+      <x:c r="G45" t="str">
+        <x:v>17308.027292000002</x:v>
+      </x:c>
+      <x:c r="H45" t="str">
+        <x:v>16997.736378677946</x:v>
+      </x:c>
+      <x:c r="I45" t="str">
+        <x:v>0.0</x:v>
       </x:c>
       <x:c r="J45" t="str">
-        <x:v>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</x:v>
+        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
       </x:c>
       <x:c r="K45" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B46" t="str">
-        <x:v>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Petroleum coke</x:v>
+        <x:v>Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat</x:v>
       </x:c>
       <x:c r="C46" t="str">
-        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Petroleum coke (canonical LEAP sector candidates=['CHP interim/Processes/CHP interim/Feedstock Fuels', 'CHP interim/Processes/CHP interim', 'CHP interim/Processes', 'CHP interim']; fuel='Petroleum coke')</x:v>
-      </x:c>
-      <x:c r="D46" t="str">
-        <x:v>20_USA</x:v>
-      </x:c>
+        <x:v>Material ESTO evidence is limited to 2023 for 05_PRC (China), at -1704.741122 PJ. This is arguably not a genuine electricity-plant feedstock value because the heat input is better suited to CHP. Retain disabled pending routing confirmation; the 2026 vintage has no material 2024 value.</x:v>
+      </x:c>
+      <x:c r="D46"/>
       <x:c r="E46"/>
-      <x:c r="F46"/>
-      <x:c r="G46"/>
-      <x:c r="H46"/>
-      <x:c r="I46"/>
-      <x:c r="J46"/>
+      <x:c r="F46" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G46" t="str">
+        <x:v>-1704.741122</x:v>
+      </x:c>
+      <x:c r="H46" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I46" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J46" t="str">
+        <x:v>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</x:v>
+      </x:c>
       <x:c r="K46" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>DISABLED — no trigger across audited vintages</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B47" t="str">
-        <x:v>Transformation\Coke ovens\Processes\Coke ovens\Feedstock Fuels\Coke oven coke</x:v>
+        <x:v>Transformation\Gas works plants\Processes\Gas works plants\Auxiliary Fuels\Anthracite</x:v>
       </x:c>
       <x:c r="C47" t="str">
-        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero/coverage transformation rows for 11_MEX, but the selected Mexico template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Coke ovens\Processes\Coke ovens\Feedstock Fuels\Coke oven coke (canonical LEAP sector candidates=['Coke ovens/Processes/Coke ovens/Feedstock Fuels', 'Coke ovens/Processes/Coke ovens', 'Coke ovens/Processes', 'Coke ovens']; fuel='Coke oven coke')</x:v>
-      </x:c>
-      <x:c r="D47" t="str">
-        <x:v>11_MEX</x:v>
-      </x:c>
+        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
+      </x:c>
+      <x:c r="D47" t="str"/>
       <x:c r="E47"/>
-      <x:c r="F47"/>
-      <x:c r="G47"/>
-      <x:c r="H47"/>
-      <x:c r="I47"/>
+      <x:c r="F47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I47" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J47" t="str">
-        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
+        <x:v>Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
       </x:c>
       <x:c r="K47" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>DISABLED — zero across maintained sources</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="4" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B48" t="str">
-        <x:v>Transformation\Electricity interim\Processes\Electricity interim\Feedstock Fuels\Heat</x:v>
+        <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>Material ESTO evidence is limited to 2023 for 05_PRC (China), at -1704.741122 PJ. This is arguably not a genuine electricity-plant feedstock value because the heat input is better suited to CHP. Retain disabled pending routing confirmation; the 2026 vintage has no material 2024 value.</x:v>
+        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
       </x:c>
       <x:c r="D48"/>
       <x:c r="E48"/>
-      <x:c r="F48" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G48" t="n">
-        <x:v>-1704.741122</x:v>
-      </x:c>
-      <x:c r="H48" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I48" t="n">
+      <x:c r="F48" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G48" t="str">
+        <x:v>-3.060635</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>-2.743651908</x:v>
+      </x:c>
+      <x:c r="I48" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J48" t="str">
         <x:v>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="K48" t="str">
-        <x:v>DISABLED — no trigger across audited vintages</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -1728,53 +1884,61 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B49" t="str">
-        <x:v>Transformation\Gas works plants\Processes\Gas works plants\Auxiliary Fuels\Anthracite</x:v>
+        <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Gas works plants\Processes\Gas works plants\Auxiliary Fuels\Anthracite (canonical LEAP sector candidates=['Gas works plants/Processes/Gas works plants/Auxiliary Fuels', 'Gas works plants/Processes/Gas works plants', 'Gas works plants/Processes', 'Gas works plants']; fuel='Anthracite')</x:v>
-      </x:c>
-      <x:c r="D49" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
+      </x:c>
+      <x:c r="D49"/>
       <x:c r="E49"/>
-      <x:c r="F49"/>
-      <x:c r="G49"/>
-      <x:c r="H49"/>
-      <x:c r="I49"/>
-      <x:c r="J49"/>
+      <x:c r="F49" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G49" t="str">
+        <x:v>-0.1022</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>-0.102199788</x:v>
+      </x:c>
+      <x:c r="I49" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J49" t="str">
+        <x:v>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</x:v>
+      </x:c>
       <x:c r="K49" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B50" t="str">
-        <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat</x:v>
+        <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Petroleum coke</x:v>
       </x:c>
       <x:c r="C50" t="str">
-        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
-      </x:c>
-      <x:c r="D50"/>
+        <x:v>Absent from the PRC clean-slate template, but nonzero source evidence exists: 2022 Current Accounts feedstock share and nonzero Reference/Target projected shares from 2023 onward. Retain as a PRC-only exception until the template branch is created/exported. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
+      </x:c>
+      <x:c r="D50" t="str"/>
       <x:c r="E50"/>
       <x:c r="F50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="G50" t="n">
-        <x:v>-3.060635</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="H50" t="n">
-        <x:v>-2.743651908</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I50" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J50" t="str">
-        <x:v>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</x:v>
+        <x:v>2024-vintage PRC baseline run: nonzero 2022 and projected feedstock-share evidence; branch absent from PRC clean slate 24_08.xlsx. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
       </x:c>
       <x:c r="K50" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>DISABLED — zero across maintained sources</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -1782,30 +1946,32 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B51" t="str">
-        <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products</x:v>
+        <x:v>Transformation\Non specified transformation\Output Fuels\Additives and oxygenates</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
-      </x:c>
-      <x:c r="D51"/>
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Non specified transformation\Output Fuels\Additives and oxygenates (canonical LEAP sector candidates=['Non specified transformation/Output Fuels', 'Non specified transformation']; fuel='Additives and oxygenates')</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>02_BD|20_USA</x:v>
+      </x:c>
       <x:c r="E51"/>
-      <x:c r="F51" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G51" t="n">
-        <x:v>-0.1022</x:v>
-      </x:c>
-      <x:c r="H51" t="n">
-        <x:v>-0.102199788</x:v>
-      </x:c>
-      <x:c r="I51" t="n">
-        <x:v>0</x:v>
+      <x:c r="F51" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G51" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H51" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I51" t="str">
+        <x:v>476.16231608118</x:v>
       </x:c>
       <x:c r="J51" t="str">
-        <x:v>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</x:v>
+        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>CONFIRMED NONZERO</x:v>
+        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1813,21 +1979,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B52" t="str">
-        <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Petroleum coke</x:v>
+        <x:v>Transformation\Non specified transformation\Output Fuels\Refinery feedstocks</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>Absent from the PRC clean-slate template, but nonzero source evidence exists: 2022 Current Accounts feedstock share and nonzero Reference/Target projected shares from 2023 onward. Retain as a PRC-only exception until the template branch is created/exported. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Petroleum coke (canonical LEAP sector candidates=['Heat plant interim/Processes/Heat plant interim/Feedstock Fuels', 'Heat plant interim/Processes/Heat plant interim', 'Heat plant interim/Processes', 'Heat plant interim']; fuel='Petroleum coke')</x:v>
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Non specified transformation\Output Fuels\Refinery feedstocks (canonical LEAP sector candidates=['Non specified transformation/Output Fuels', 'Non specified transformation']; fuel='Refinery feedstocks')</x:v>
       </x:c>
       <x:c r="D52" t="str">
-        <x:v>05_PRC</x:v>
+        <x:v>02_BD|20_USA</x:v>
       </x:c>
       <x:c r="E52"/>
-      <x:c r="F52"/>
-      <x:c r="G52"/>
-      <x:c r="H52"/>
-      <x:c r="I52"/>
+      <x:c r="F52" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="G52" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="H52" t="str">
+        <x:v>0.0</x:v>
+      </x:c>
+      <x:c r="I52" t="str">
+        <x:v>476.16231608118</x:v>
+      </x:c>
       <x:c r="J52" t="str">
-        <x:v>2024-vintage PRC baseline run: nonzero 2022 and projected feedstock-share evidence; branch absent from PRC clean slate 24_08.xlsx.</x:v>
+        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
       </x:c>
       <x:c r="K52" t="str">
         <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
@@ -1838,19 +2012,27 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B53" t="str">
-        <x:v>Transformation\Non specified transformation\Output Fuels\Additives and oxygenates</x:v>
+        <x:v>Transformation\Transfers unallocated\Output Fuels\Natural gas liquids</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Non specified transformation\Output Fuels\Additives and oxygenates (canonical LEAP sector candidates=['Non specified transformation/Output Fuels', 'Non specified transformation']; fuel='Additives and oxygenates')</x:v>
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated transfer rows for 19_THA, but the selected Thailand template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Output Fuels\Natural gas liquids (canonical LEAP sector candidates=['Transfers unallocated/Output Fuels', 'Transfers unallocated']; fuel='Natural gas liquids')</x:v>
       </x:c>
       <x:c r="D53" t="str">
-        <x:v>02_BD|20_USA</x:v>
+        <x:v>19_THA</x:v>
       </x:c>
       <x:c r="E53"/>
-      <x:c r="F53"/>
-      <x:c r="G53"/>
-      <x:c r="H53"/>
-      <x:c r="I53"/>
+      <x:c r="F53" t="str">
+        <x:v>-7489.010503</x:v>
+      </x:c>
+      <x:c r="G53" t="str">
+        <x:v>-7974.135619999999</x:v>
+      </x:c>
+      <x:c r="H53" t="str">
+        <x:v>-8835.851996079695</x:v>
+      </x:c>
+      <x:c r="I53" t="str">
+        <x:v>-7183.419949661826</x:v>
+      </x:c>
       <x:c r="J53" t="str">
         <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
       </x:c>
@@ -1863,21 +2045,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B54" t="str">
-        <x:v>Transformation\Non specified transformation\Output Fuels\Refinery feedstocks</x:v>
+        <x:v>Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Petroleum coke</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Non specified transformation\Output Fuels\Refinery feedstocks (canonical LEAP sector candidates=['Non specified transformation/Output Fuels', 'Non specified transformation']; fuel='Refinery feedstocks')</x:v>
+        <x:v>Absent from the PRC clean-slate template, but nonzero 2022 Current Accounts feedstock-share evidence exists. Retain as a PRC-only exception until the template branch is created/exported. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Petroleum coke (canonical LEAP sector candidates=['Transfers unallocated/Processes/Transfers unallocated/Feedstock Fuels', 'Transfers unallocated/Processes/Transfers unallocated', 'Transfers unallocated/Processes', 'Transfers unallocated']; fuel='Petroleum coke')</x:v>
       </x:c>
       <x:c r="D54" t="str">
-        <x:v>02_BD|20_USA</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E54"/>
-      <x:c r="F54"/>
-      <x:c r="G54"/>
-      <x:c r="H54"/>
-      <x:c r="I54"/>
+      <x:c r="F54" t="str">
+        <x:v>156.630428</x:v>
+      </x:c>
+      <x:c r="G54" t="str">
+        <x:v>157.66611899999998</x:v>
+      </x:c>
+      <x:c r="H54" t="str">
+        <x:v>162.03822076856</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>-522.47987829</x:v>
+      </x:c>
       <x:c r="J54" t="str">
-        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
+        <x:v>2024-vintage PRC baseline run: nonzero 2022 feedstock-share evidence; no projected transfer-share rows were emitted.</x:v>
       </x:c>
       <x:c r="K54" t="str">
         <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
@@ -1888,21 +2078,29 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B55" t="str">
-        <x:v>Transformation\Transfers unallocated\Output Fuels\Natural gas liquids</x:v>
+        <x:v>Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Refinery gas not liquefied</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated transfer rows for 19_THA, but the selected Thailand template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Output Fuels\Natural gas liquids (canonical LEAP sector candidates=['Transfers unallocated/Output Fuels', 'Transfers unallocated']; fuel='Natural gas liquids')</x:v>
+        <x:v>Absent from the PRC clean-slate template, but nonzero 2022 Current Accounts feedstock-share evidence exists. Retain as a PRC-only exception until the template branch is created/exported. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Refinery gas not liquefied (canonical LEAP sector candidates=['Transfers unallocated/Processes/Transfers unallocated/Feedstock Fuels', 'Transfers unallocated/Processes/Transfers unallocated', 'Transfers unallocated/Processes', 'Transfers unallocated']; fuel='Refinery gas not liquefied')</x:v>
       </x:c>
       <x:c r="D55" t="str">
-        <x:v>19_THA</x:v>
+        <x:v>05_PRC</x:v>
       </x:c>
       <x:c r="E55"/>
-      <x:c r="F55"/>
-      <x:c r="G55"/>
-      <x:c r="H55"/>
-      <x:c r="I55"/>
+      <x:c r="F55" t="str">
+        <x:v>197.61872300000005</x:v>
+      </x:c>
+      <x:c r="G55" t="str">
+        <x:v>217.28544200000005</x:v>
+      </x:c>
+      <x:c r="H55" t="str">
+        <x:v>182.51084353280004</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>210.05175600000004</x:v>
+      </x:c>
       <x:c r="J55" t="str">
-        <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
+        <x:v>2024-vintage PRC baseline run: nonzero 2022 feedstock-share evidence; no projected transfer-share rows were emitted.</x:v>
       </x:c>
       <x:c r="K55" t="str">
         <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
@@ -1910,76 +2108,60 @@
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B56" t="str">
-        <x:v>Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Petroleum coke</x:v>
+        <x:v>Transformation\Gas to liquids plants\Output Fuels\Refinery gas not liquefied</x:v>
       </x:c>
       <x:c r="C56" t="str">
-        <x:v>Absent from the PRC clean-slate template, but nonzero 2022 Current Accounts feedstock-share evidence exists. Retain as a PRC-only exception until the template branch is created/exported. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Petroleum coke (canonical LEAP sector candidates=['Transfers unallocated/Processes/Transfers unallocated/Feedstock Fuels', 'Transfers unallocated/Processes/Transfers unallocated', 'Transfers unallocated/Processes', 'Transfers unallocated']; fuel='Petroleum coke')</x:v>
-      </x:c>
-      <x:c r="D56" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
+      </x:c>
+      <x:c r="D56" t="str"/>
       <x:c r="E56"/>
-      <x:c r="F56"/>
-      <x:c r="G56"/>
-      <x:c r="H56"/>
-      <x:c r="I56"/>
+      <x:c r="F56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I56" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J56" t="str">
-        <x:v>2024-vintage PRC baseline run: nonzero 2022 feedstock-share evidence; no projected transfer-share rows were emitted.</x:v>
+        <x:v>Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
       </x:c>
       <x:c r="K56" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>DISABLED — zero across maintained sources</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
-      <x:c r="A57" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B57" t="str">
-        <x:v>Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Refinery gas not liquefied</x:v>
-      </x:c>
-      <x:c r="C57" t="str">
-        <x:v>Absent from the PRC clean-slate template, but nonzero 2022 Current Accounts feedstock-share evidence exists. Retain as a PRC-only exception until the template branch is created/exported. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Refinery gas not liquefied (canonical LEAP sector candidates=['Transfers unallocated/Processes/Transfers unallocated/Feedstock Fuels', 'Transfers unallocated/Processes/Transfers unallocated', 'Transfers unallocated/Processes', 'Transfers unallocated']; fuel='Refinery gas not liquefied')</x:v>
-      </x:c>
-      <x:c r="D57" t="str">
-        <x:v>05_PRC</x:v>
-      </x:c>
+      <x:c r="A57"/>
+      <x:c r="B57"/>
+      <x:c r="C57"/>
+      <x:c r="D57"/>
       <x:c r="E57"/>
       <x:c r="F57"/>
       <x:c r="G57"/>
       <x:c r="H57"/>
       <x:c r="I57"/>
-      <x:c r="J57" t="str">
-        <x:v>2024-vintage PRC baseline run: nonzero 2022 feedstock-share evidence; no projected transfer-share rows were emitted.</x:v>
-      </x:c>
-      <x:c r="K57" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
-      </x:c>
+      <x:c r="J57"/>
+      <x:c r="K57"/>
     </x:row>
     <x:row r="58">
-      <x:c r="A58" s="4" t="b">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B58" t="str">
-        <x:v>Transformation\Gas to liquids plants\Output Fuels\Refinery gas not liquefied</x:v>
-      </x:c>
-      <x:c r="C58" t="str">
-        <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Gas to liquids plants\Output Fuels\Refinery gas not liquefied (canonical LEAP sector candidates=['Gas to liquids plants/Output Fuels', 'Gas to liquids plants']; fuel='Refinery gas not liquefied')</x:v>
-      </x:c>
-      <x:c r="D58" t="str">
-        <x:v>10_MAS</x:v>
-      </x:c>
+      <x:c r="A58"/>
+      <x:c r="B58"/>
+      <x:c r="C58"/>
+      <x:c r="D58"/>
       <x:c r="E58"/>
       <x:c r="F58"/>
       <x:c r="G58"/>
       <x:c r="H58"/>
       <x:c r="I58"/>
       <x:c r="J58"/>
-      <x:c r="K58" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
-      </x:c>
+      <x:c r="K58"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="R843b68bb88c445b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Rd24aa858a93a47d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="R39259314f7bf4a3d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Re2b11773dd774cb9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,7 +421,7 @@
         <x:v>Demand\All demand aggregated\Non Energy Use\Blast furnace gas</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Blast furnace gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D3" t="str">
         <x:v>05_PRC</x:v>
@@ -454,7 +454,7 @@
         <x:v>Demand\All demand aggregated\Non Energy Use\Gas works gas</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Gas works gas (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D4" t="str">
         <x:v>05_PRC</x:v>
@@ -487,7 +487,7 @@
         <x:v>Demand\All demand aggregated\Non Energy Use\Hydrogen</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Hydrogen (sector='Non Energy Use'; fuel='Hydrogen'; 9th sector='Non Energy Use')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|10_MAS|15_PHL|16_RUS|20_USA|21_VN. 2022 base final stage: found not needed for 05_PRC|19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 01_AUS|05_PRC|10_MAS|15_PHL|19_THA|20_USA|21_VN. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="D5" t="str">
         <x:v>01_AUS|05_PRC|10_MAS|15_PHL|16_RUS|19_THA|20_USA|21_VN</x:v>
@@ -520,7 +520,7 @@
         <x:v>Demand\All demand aggregated\Non Energy Use\Other recovered gases</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\All demand aggregated\Non Energy Use\Other recovered gases (sector='Non Energy Use'; 9th sector='Non Energy Use')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D6" t="str">
         <x:v>05_PRC</x:v>
@@ -718,7 +718,7 @@
         <x:v>Demand\Other loss and own use\Coal mines\Lubricants</x:v>
       </x:c>
       <x:c r="C12" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Coal mines\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Coal mines', 'Other loss and own use']; fuel='Lubricants')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D12" t="str">
         <x:v>05_PRC</x:v>
@@ -740,7 +740,7 @@
         <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K12" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1445,7 +1445,7 @@
         <x:v>Demand\Other loss and own use\Oil and gas extraction\Lubricants</x:v>
       </x:c>
       <x:c r="C35" t="str">
-        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Demand\Other loss and own use\Oil and gas extraction\Lubricants (canonical LEAP sector candidates=['Other loss and own use/Oil and gas extraction', 'Other loss and own use']; fuel='Lubricants')</x:v>
+        <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="D35" t="str">
         <x:v>05_PRC</x:v>
@@ -1467,7 +1467,7 @@
         <x:v>2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC.</x:v>
       </x:c>
       <x:c r="K35" t="str">
-        <x:v>MAPPING INCOMPLETE — seed triggered</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -1699,7 +1699,7 @@
         <x:v>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat (sector='CHP interim'; 9th sector='CHP interim') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
+        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation.</x:v>
       </x:c>
       <x:c r="D43"/>
       <x:c r="E43"/>
@@ -1761,7 +1761,7 @@
         <x:v>Transformation\Coke ovens\Processes\Coke ovens\Feedstock Fuels\Coke oven coke</x:v>
       </x:c>
       <x:c r="C45" t="str">
-        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero/coverage transformation rows for 11_MEX, but the selected Mexico template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Coke ovens\Processes\Coke ovens\Feedstock Fuels\Coke oven coke (canonical LEAP sector candidates=['Coke ovens/Processes/Coke ovens/Feedstock Fuels', 'Coke ovens/Processes/Coke ovens', 'Coke ovens/Processes', 'Coke ovens']; fuel='Coke oven coke')</x:v>
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero/coverage transformation rows for 11_MEX, but the selected Mexico template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists.</x:v>
       </x:c>
       <x:c r="D45" t="str">
         <x:v>11_MEX</x:v>
@@ -1783,7 +1783,7 @@
         <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
       </x:c>
       <x:c r="K45" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -1814,7 +1814,7 @@
         <x:v>2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding).</x:v>
       </x:c>
       <x:c r="K46" t="str">
-        <x:v>DISABLED — no trigger across audited vintages</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -1887,7 +1887,7 @@
         <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products (fuel='Peat products') Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
+        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation.</x:v>
       </x:c>
       <x:c r="D49"/>
       <x:c r="E49"/>
@@ -1949,7 +1949,7 @@
         <x:v>Transformation\Non specified transformation\Output Fuels\Additives and oxygenates</x:v>
       </x:c>
       <x:c r="C51" t="str">
-        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Non specified transformation\Output Fuels\Additives and oxygenates (canonical LEAP sector candidates=['Non specified transformation/Output Fuels', 'Non specified transformation']; fuel='Additives and oxygenates')</x:v>
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists.</x:v>
       </x:c>
       <x:c r="D51" t="str">
         <x:v>02_BD|20_USA</x:v>
@@ -1971,7 +1971,7 @@
         <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
       </x:c>
       <x:c r="K51" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -1982,7 +1982,7 @@
         <x:v>Transformation\Non specified transformation\Output Fuels\Refinery feedstocks</x:v>
       </x:c>
       <x:c r="C52" t="str">
-        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Non specified transformation\Output Fuels\Refinery feedstocks (canonical LEAP sector candidates=['Non specified transformation/Output Fuels', 'Non specified transformation']; fuel='Refinery feedstocks')</x:v>
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated nonzero transformation rows for 02_BD and 20_USA, but the selected economy templates do not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists.</x:v>
       </x:c>
       <x:c r="D52" t="str">
         <x:v>02_BD|20_USA</x:v>
@@ -2004,7 +2004,7 @@
         <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
       </x:c>
       <x:c r="K52" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -2015,7 +2015,7 @@
         <x:v>Transformation\Transfers unallocated\Output Fuels\Natural gas liquids</x:v>
       </x:c>
       <x:c r="C53" t="str">
-        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated transfer rows for 19_THA, but the selected Thailand template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Output Fuels\Natural gas liquids (canonical LEAP sector candidates=['Transfers unallocated/Output Fuels', 'Transfers unallocated']; fuel='Natural gas liquids')</x:v>
+        <x:v>Reviewed from baseline-seed run run_583459 (2026-08-25): generated transfer rows for 19_THA, but the selected Thailand template does not expose this branch. Treat as a reviewed warning-only exception pending template creation or an explicit workflow remap; do not interpret this row as evidence that the LEAP branch currently exists.</x:v>
       </x:c>
       <x:c r="D53" t="str">
         <x:v>19_THA</x:v>
@@ -2037,7 +2037,7 @@
         <x:v>2026-08-25 final run: material missing-branch finding; exception requested for warning-only tracking pending template/workflow decision.</x:v>
       </x:c>
       <x:c r="K53" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -2048,7 +2048,7 @@
         <x:v>Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Petroleum coke</x:v>
       </x:c>
       <x:c r="C54" t="str">
-        <x:v>Absent from the PRC clean-slate template, but nonzero 2022 Current Accounts feedstock-share evidence exists. Retain as a PRC-only exception until the template branch is created/exported. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Petroleum coke (canonical LEAP sector candidates=['Transfers unallocated/Processes/Transfers unallocated/Feedstock Fuels', 'Transfers unallocated/Processes/Transfers unallocated', 'Transfers unallocated/Processes', 'Transfers unallocated']; fuel='Petroleum coke')</x:v>
+        <x:v>Absent from the PRC clean-slate template, but nonzero 2022 Current Accounts feedstock-share evidence exists. Retain as a PRC-only exception until the template branch is created/exported.</x:v>
       </x:c>
       <x:c r="D54" t="str">
         <x:v>05_PRC</x:v>
@@ -2070,7 +2070,7 @@
         <x:v>2024-vintage PRC baseline run: nonzero 2022 feedstock-share evidence; no projected transfer-share rows were emitted.</x:v>
       </x:c>
       <x:c r="K54" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -2081,7 +2081,7 @@
         <x:v>Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Refinery gas not liquefied</x:v>
       </x:c>
       <x:c r="C55" t="str">
-        <x:v>Absent from the PRC clean-slate template, but nonzero 2022 Current Accounts feedstock-share evidence exists. Retain as a PRC-only exception until the template branch is created/exported. Materiality mapping needs review: Registry path needs an explicit source mapping before materiality can be refreshed: Transformation\Transfers unallocated\Processes\Transfers unallocated\Feedstock Fuels\Refinery gas not liquefied (canonical LEAP sector candidates=['Transfers unallocated/Processes/Transfers unallocated/Feedstock Fuels', 'Transfers unallocated/Processes/Transfers unallocated', 'Transfers unallocated/Processes', 'Transfers unallocated']; fuel='Refinery gas not liquefied')</x:v>
+        <x:v>Absent from the PRC clean-slate template, but nonzero 2022 Current Accounts feedstock-share evidence exists. Retain as a PRC-only exception until the template branch is created/exported.</x:v>
       </x:c>
       <x:c r="D55" t="str">
         <x:v>05_PRC</x:v>
@@ -2103,7 +2103,7 @@
         <x:v>2024-vintage PRC baseline run: nonzero 2022 feedstock-share evidence; no projected transfer-share rows were emitted.</x:v>
       </x:c>
       <x:c r="K55" t="str">
-        <x:v>MAPPING INCOMPLETE — source mapping required</x:v>
+        <x:v>CONFIRMED NONZERO</x:v>
       </x:c>
     </x:row>
     <x:row r="56">

--- a/config/baseline_seed_validation_exception_sets.xlsx
+++ b/config/baseline_seed_validation_exception_sets.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="R39259314f7bf4a3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="Re2b11773dd774cb9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_exceptions" sheetId="1" r:id="Refe83dfa27204f96"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="2" r:id="R0c0ceade854243c9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -555,7 +555,7 @@
       <x:c r="C7" t="str">
         <x:v>The sector-split aggregated-demand workflow can produce a small Other sector amount for this fuel, but the economy templates do not expose that branch; the values are immaterial and are intentionally left out. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D7" t="str"/>
+      <x:c r="D7"/>
       <x:c r="E7" t="str">
         <x:v>01_AUS|02_BD|05_PRC|10_MAS|11_MEX|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN</x:v>
       </x:c>
@@ -852,7 +852,7 @@
       <x:c r="C16" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D16" t="str"/>
+      <x:c r="D16"/>
       <x:c r="E16"/>
       <x:c r="F16" t="n">
         <x:v>0</x:v>
@@ -883,7 +883,7 @@
       <x:c r="C17" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D17" t="str"/>
+      <x:c r="D17"/>
       <x:c r="E17"/>
       <x:c r="F17" t="n">
         <x:v>0</x:v>
@@ -914,7 +914,7 @@
       <x:c r="C18" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D18" t="str"/>
+      <x:c r="D18"/>
       <x:c r="E18"/>
       <x:c r="F18" t="n">
         <x:v>0</x:v>
@@ -978,7 +978,7 @@
       <x:c r="C20" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D20" t="str"/>
+      <x:c r="D20"/>
       <x:c r="E20"/>
       <x:c r="F20" t="n">
         <x:v>0</x:v>
@@ -1042,7 +1042,7 @@
       <x:c r="C22" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D22" t="str"/>
+      <x:c r="D22"/>
       <x:c r="E22"/>
       <x:c r="F22" t="n">
         <x:v>0</x:v>
@@ -1073,7 +1073,7 @@
       <x:c r="C23" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D23" t="str"/>
+      <x:c r="D23"/>
       <x:c r="E23"/>
       <x:c r="F23" t="n">
         <x:v>0</x:v>
@@ -1104,7 +1104,7 @@
       <x:c r="C24" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D24" t="str"/>
+      <x:c r="D24"/>
       <x:c r="E24"/>
       <x:c r="F24" t="n">
         <x:v>0</x:v>
@@ -1135,7 +1135,7 @@
       <x:c r="C25" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D25" t="str"/>
+      <x:c r="D25"/>
       <x:c r="E25"/>
       <x:c r="F25" t="n">
         <x:v>0</x:v>
@@ -1166,7 +1166,7 @@
       <x:c r="C26" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D26" t="str"/>
+      <x:c r="D26"/>
       <x:c r="E26"/>
       <x:c r="F26" t="n">
         <x:v>0</x:v>
@@ -1197,7 +1197,7 @@
       <x:c r="C27" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 05_PRC (no material unknown-path finding). 2026 preliminary final stage: triggered for 05_PRC. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D27" t="str"/>
+      <x:c r="D27"/>
       <x:c r="E27"/>
       <x:c r="F27" t="n">
         <x:v>0</x:v>
@@ -1228,7 +1228,7 @@
       <x:c r="C28" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D28" t="str"/>
+      <x:c r="D28"/>
       <x:c r="E28"/>
       <x:c r="F28" t="n">
         <x:v>0</x:v>
@@ -1259,7 +1259,7 @@
       <x:c r="C29" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS|16_RUS. 2026 preliminary final stage: triggered for 01_AUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D29" t="str"/>
+      <x:c r="D29"/>
       <x:c r="E29"/>
       <x:c r="F29" t="n">
         <x:v>0</x:v>
@@ -1480,7 +1480,7 @@
       <x:c r="C36" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 01_AUS. 2026 preliminary final stage: triggered for 01_AUS. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D36" t="str"/>
+      <x:c r="D36"/>
       <x:c r="E36"/>
       <x:c r="F36" t="n">
         <x:v>0</x:v>
@@ -1544,7 +1544,7 @@
       <x:c r="C38" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D38" t="str"/>
+      <x:c r="D38"/>
       <x:c r="E38"/>
       <x:c r="F38" t="n">
         <x:v>0</x:v>
@@ -1575,7 +1575,7 @@
       <x:c r="C39" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 19_THA (no material unknown-path finding). 2026 preliminary final stage: triggered for 19_THA. Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D39" t="str"/>
+      <x:c r="D39"/>
       <x:c r="E39"/>
       <x:c r="F39" t="n">
         <x:v>0</x:v>
@@ -1639,7 +1639,7 @@
       <x:c r="C41" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D41" t="str"/>
+      <x:c r="D41"/>
       <x:c r="E41"/>
       <x:c r="F41" t="n">
         <x:v>0</x:v>
@@ -1670,7 +1670,7 @@
       <x:c r="C42" t="str">
         <x:v>Automatically recorded from material baseline-seed validation; review/create in LEAP when appropriate. Warnings only: this row never blocks seed generation. Relevance audit: 2022 base final stage: triggered for 16_RUS. 2026 preliminary final stage: found not needed for 16_RUS (no material unknown-path finding). Disabled 2026-09-01: the current producing workflow emits no nonzero value for this economy/branch across the configured horizon. This is a stale historical exception, not a missing LEAP template branch.</x:v>
       </x:c>
-      <x:c r="D42" t="str"/>
+      <x:c r="D42"/>
       <x:c r="E42"/>
       <x:c r="F42" t="n">
         <x:v>0</x:v>
@@ -1693,13 +1693,13 @@
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B43" t="str">
         <x:v>Transformation\CHP interim\Processes\CHP interim\Feedstock Fuels\Peat</x:v>
       </x:c>
       <x:c r="C43" t="str">
-        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation.</x:v>
+        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. No target economy is missing this branch; source totals alone do not make it a seed exception.</x:v>
       </x:c>
       <x:c r="D43"/>
       <x:c r="E43"/>
@@ -1732,7 +1732,7 @@
       <x:c r="C44" t="str">
         <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
       </x:c>
-      <x:c r="D44" t="str"/>
+      <x:c r="D44"/>
       <x:c r="E44"/>
       <x:c r="F44" t="n">
         <x:v>0</x:v>
@@ -1827,7 +1827,7 @@
       <x:c r="C47" t="str">
         <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
       </x:c>
-      <x:c r="D47" t="str"/>
+      <x:c r="D47"/>
       <x:c r="E47"/>
       <x:c r="F47" t="n">
         <x:v>0</x:v>
@@ -1850,13 +1850,13 @@
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B48" t="str">
         <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat</x:v>
       </x:c>
       <x:c r="C48" t="str">
-        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy.</x:v>
+        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. Relevance audit: 2022 base final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). 2026 preliminary final stage: found not needed for 01_AUS|02_BD|05_PRC|10_MAS|11_MEX|12_NZ|13_PNG|15_PHL|16_RUS|19_THA|20_USA|21_VN (no material unknown-path finding). Disabled after the completed all-vintage relevance audit: it did not trigger for any previously marked economy. No target economy is missing this branch; source totals alone do not make it a seed exception.</x:v>
       </x:c>
       <x:c r="D48"/>
       <x:c r="E48"/>
@@ -1881,13 +1881,13 @@
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="4" t="b">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B49" t="str">
         <x:v>Transformation\Heat plant interim\Processes\Heat plant interim\Feedstock Fuels\Peat products</x:v>
       </x:c>
       <x:c r="C49" t="str">
-        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation.</x:v>
+        <x:v>Temporary interim-power placeholder: absent from current LEAP templates. Keep BranchID 99 until a real branch is created/exported; warnings-only and never blocks seed generation. No target economy is missing this branch; source totals alone do not make it a seed exception.</x:v>
       </x:c>
       <x:c r="D49"/>
       <x:c r="E49"/>
@@ -1920,7 +1920,7 @@
       <x:c r="C50" t="str">
         <x:v>Absent from the PRC clean-slate template, but nonzero source evidence exists: 2022 Current Accounts feedstock share and nonzero Reference/Target projected shares from 2023 onward. Retain as a PRC-only exception until the template branch is created/exported. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
       </x:c>
-      <x:c r="D50" t="str"/>
+      <x:c r="D50"/>
       <x:c r="E50"/>
       <x:c r="F50" t="n">
         <x:v>0</x:v>
@@ -2116,7 +2116,7 @@
       <x:c r="C56" t="str">
         <x:v>Automatically recorded from baseline-seed validation; review/create in LEAP when appropriate. Disabled 2026-09-01: all maintained ESTO and Ninth materiality values are zero and no completed relevance audit recorded a material trigger.</x:v>
       </x:c>
-      <x:c r="D56" t="str"/>
+      <x:c r="D56"/>
       <x:c r="E56"/>
       <x:c r="F56" t="n">
         <x:v>0</x:v>
